--- a/results/tables/Seroneutralization_Analysis.xlsx
+++ b/results/tables/Seroneutralization_Analysis.xlsx
@@ -11,13 +11,14 @@
     <sheet name="Resumen_Estadistico" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="ANOVA_LMM" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="EMMeans" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Comparaciones_Pares" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comparaciones_Grupos" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comparaciones_Virus" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
   <si>
     <t xml:space="preserve">Section</t>
   </si>
@@ -251,6 +252,24 @@
   </si>
   <si>
     <t xml:space="preserve">100 µg - Comm.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B - E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C - D</t>
+  </si>
+  <si>
+    <t xml:space="preserve">C - E</t>
+  </si>
+  <si>
+    <t xml:space="preserve">D - E</t>
   </si>
 </sst>
 </file>
@@ -666,10 +685,10 @@
         <v>19</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E2" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
     </row>
     <row r="3">
@@ -683,10 +702,10 @@
         <v>19</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E3" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
     </row>
     <row r="4">
@@ -1057,10 +1076,10 @@
         <v>46</v>
       </c>
       <c r="D25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E25" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
     </row>
     <row r="26">
@@ -1074,10 +1093,10 @@
         <v>46</v>
       </c>
       <c r="D26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E26" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
     </row>
     <row r="27">
@@ -1448,10 +1467,10 @@
         <v>47</v>
       </c>
       <c r="D48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E48" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
     </row>
     <row r="49">
@@ -1465,10 +1484,10 @@
         <v>47</v>
       </c>
       <c r="D49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E49" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
     </row>
     <row r="50">
@@ -1839,10 +1858,10 @@
         <v>48</v>
       </c>
       <c r="D71" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E71" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
     </row>
     <row r="72">
@@ -1856,10 +1875,10 @@
         <v>48</v>
       </c>
       <c r="D72" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E72" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
     </row>
     <row r="73">
@@ -2267,7 +2286,7 @@
         <v>2</v>
       </c>
       <c r="D2" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -2276,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -2397,7 +2416,7 @@
         <v>2</v>
       </c>
       <c r="D7" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
@@ -2406,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="G7" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
       <c r="H7" t="n">
         <v>0</v>
@@ -2527,7 +2546,7 @@
         <v>2</v>
       </c>
       <c r="D12" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -2536,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="G12" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
       <c r="H12" t="n">
         <v>0</v>
@@ -2657,7 +2676,7 @@
         <v>2</v>
       </c>
       <c r="D17" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -2666,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>3.32192809488736</v>
+        <v>2.32192809488736</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -3871,4 +3890,590 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s">
+        <v>68</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" t="s">
+        <v>65</v>
+      </c>
+      <c r="F1" t="s">
+        <v>70</v>
+      </c>
+      <c r="G1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>78</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="C2" t="n">
+        <v>0.452748176400114</v>
+      </c>
+      <c r="D2" t="n">
+        <v>0.268987470711748</v>
+      </c>
+      <c r="E2" t="n">
+        <v>50.9999999999994</v>
+      </c>
+      <c r="F2" t="n">
+        <v>1.68315711955702</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.324422253632744</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" t="n">
+        <v>0.0231199405972752</v>
+      </c>
+      <c r="D3" t="n">
+        <v>0.268987470711748</v>
+      </c>
+      <c r="E3" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.0859517379605048</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.931841340786635</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s">
+        <v>80</v>
+      </c>
+      <c r="B4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0.0712673005208258</v>
+      </c>
+      <c r="D4" t="n">
+        <v>0.268987470711749</v>
+      </c>
+      <c r="E4" t="n">
+        <v>51.0000000000003</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.264946543168909</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0.931841340786635</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s">
+        <v>81</v>
+      </c>
+      <c r="B5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.429628235802839</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.268987470711748</v>
+      </c>
+      <c r="E5" t="n">
+        <v>50.9999999999995</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-1.59720538159651</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0.324422253632744</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
+        <v>82</v>
+      </c>
+      <c r="B6" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.381480875879288</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.268987470711748</v>
+      </c>
+      <c r="E6" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-1.41821057638811</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.324422253632744</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s">
+        <v>83</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.0481473599235507</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.268987470711748</v>
+      </c>
+      <c r="E7" t="n">
+        <v>51</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.178994805208404</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.931841340786635</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s">
+        <v>78</v>
+      </c>
+      <c r="B8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.25711411151231</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.355836976647779</v>
+      </c>
+      <c r="E8" t="n">
+        <v>51</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.72256153347102</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0.830522428235723</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s">
+        <v>79</v>
+      </c>
+      <c r="B9" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.33366602070371</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.355836976647778</v>
+      </c>
+      <c r="E9" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.937693501802612</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.830522428235723</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>80</v>
+      </c>
+      <c r="B10" t="s">
+        <v>30</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.423448090808604</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.355836976647778</v>
+      </c>
+      <c r="E10" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.19000586953545</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.830522428235723</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B11" t="s">
+        <v>30</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.0765519091913996</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.355836976647779</v>
+      </c>
+      <c r="E11" t="n">
+        <v>51</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.215131968331593</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.830522428235723</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B12" t="s">
+        <v>30</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.166333979296294</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.355836976647778</v>
+      </c>
+      <c r="E12" t="n">
+        <v>51</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.467444336064427</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0.830522428235723</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s">
+        <v>83</v>
+      </c>
+      <c r="B13" t="s">
+        <v>30</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.0897820701048941</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.355836976647778</v>
+      </c>
+      <c r="E13" t="n">
+        <v>51</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.252312367732834</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0.830522428235723</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
+        <v>78</v>
+      </c>
+      <c r="B14" t="s">
+        <v>35</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.570436980025377</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.268987470711749</v>
+      </c>
+      <c r="E14" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F14" t="n">
+        <v>2.12068234448238</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0.116492770998788</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="s">
+        <v>79</v>
+      </c>
+      <c r="B15" t="s">
+        <v>35</v>
+      </c>
+      <c r="C15" t="n">
+        <v>-0.0482744571466142</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.268987470711749</v>
+      </c>
+      <c r="E15" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F15" t="n">
+        <v>-0.179467307599416</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0.858281921729342</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="s">
+        <v>80</v>
+      </c>
+      <c r="B16" t="s">
+        <v>35</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.472856758837292</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.268987470711749</v>
+      </c>
+      <c r="E16" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F16" t="n">
+        <v>1.75791369607699</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0.12714397920857</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B17" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" t="n">
+        <v>-0.618711437171992</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.268987470711749</v>
+      </c>
+      <c r="E17" t="n">
+        <v>51</v>
+      </c>
+      <c r="F17" t="n">
+        <v>-2.3001496520818</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0.116492770998788</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s">
+        <v>82</v>
+      </c>
+      <c r="B18" t="s">
+        <v>35</v>
+      </c>
+      <c r="C18" t="n">
+        <v>-0.0975802211880858</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.268987470711749</v>
+      </c>
+      <c r="E18" t="n">
+        <v>51</v>
+      </c>
+      <c r="F18" t="n">
+        <v>-0.362768648405391</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0.858281921729342</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s">
+        <v>83</v>
+      </c>
+      <c r="B19" t="s">
+        <v>35</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.521131215983906</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.268987470711749</v>
+      </c>
+      <c r="E19" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F19" t="n">
+        <v>1.93738100367641</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.116492770998788</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s">
+        <v>78</v>
+      </c>
+      <c r="B20" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" t="n">
+        <v>0.271009863934635</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.410885148510435</v>
+      </c>
+      <c r="E20" t="n">
+        <v>51</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.659575710918529</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0.512493740416351</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s">
+        <v>79</v>
+      </c>
+      <c r="B21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" t="n">
+        <v>-1.8857446059221</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.410885148510435</v>
+      </c>
+      <c r="E21" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>-4.58946888871114</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.0000878123731676433</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="s">
+        <v>80</v>
+      </c>
+      <c r="B22" t="s">
+        <v>43</v>
+      </c>
+      <c r="C22" t="n">
+        <v>-1.55033518679534</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.410885148510435</v>
+      </c>
+      <c r="E22" t="n">
+        <v>50.9999999999999</v>
+      </c>
+      <c r="F22" t="n">
+        <v>-3.77315946418531</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.000631676820686117</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="s">
+        <v>81</v>
+      </c>
+      <c r="B23" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" t="n">
+        <v>-2.15675446985673</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.410885148510435</v>
+      </c>
+      <c r="E23" t="n">
+        <v>51</v>
+      </c>
+      <c r="F23" t="n">
+        <v>-5.24904459962966</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0000179503790377461</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s">
+        <v>82</v>
+      </c>
+      <c r="B24" t="s">
+        <v>43</v>
+      </c>
+      <c r="C24" t="n">
+        <v>-1.82134505072997</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.410885148510435</v>
+      </c>
+      <c r="E24" t="n">
+        <v>51</v>
+      </c>
+      <c r="F24" t="n">
+        <v>-4.43273517510384</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0.0000992076242953488</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s">
+        <v>83</v>
+      </c>
+      <c r="B25" t="s">
+        <v>43</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.335409419126761</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.410885148510435</v>
+      </c>
+      <c r="E25" t="n">
+        <v>51</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.816309424525825</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.501743773031014</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+</worksheet>
 </file>
--- a/results/tables/Seroneutralization_Analysis.xlsx
+++ b/results/tables/Seroneutralization_Analysis.xlsx
@@ -1,283 +1,306 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <workbookPr date1904="false"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e4de212fc1e0fe75/Escritorio/Analisis vacuna BVDV/Manuscrito-BVDV-challenge/results/tables/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="6" documentId="11_4154A04288EAC2C7251E9A72680C1D6BF56C1643" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{08EDD03E-5C4A-4297-AA9F-910FEA2D5C5A}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="13125" windowHeight="6105" firstSheet="0" activeTab="0"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="2" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Datos_Procesados" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Resumen_Estadistico" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="ANOVA_LMM" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="EMMeans" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Comparaciones_Grupos" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Comparaciones_Virus" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="README" sheetId="1" r:id="rId1"/>
+    <sheet name="Datos_Procesados" sheetId="2" r:id="rId2"/>
+    <sheet name="Resumen_Estadistico" sheetId="3" r:id="rId3"/>
+    <sheet name="ANOVA_LMM" sheetId="4" r:id="rId4"/>
+    <sheet name="EMMeans" sheetId="5" r:id="rId5"/>
+    <sheet name="Comparaciones_Grupos" sheetId="6" r:id="rId6"/>
+    <sheet name="Comparaciones_Virus" sheetId="7" r:id="rId7"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="84">
-  <si>
-    <t xml:space="preserve">Section</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Description</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Input Data</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log2 neutralizing antibody titers dataset</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Descriptive Stats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Summary stats by virus and group (Mean, SD, SEM, Median, IQR)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LMM ANOVA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linear Mixed-Effects Model Type III ANOVA table</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EMMeans</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Estimated Marginal Means for treatment groups</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pairwise Contrasts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pairwise comparisons (BH adjusted p-values)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Animal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Virus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Titulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Log2_Titulo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 µg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 µg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 µg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23</t>
-  </si>
-  <si>
-    <t xml:space="preserve">24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Comm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">27</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">N</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Media_Log2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SD_Log2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SEM_Log2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mediana_Log2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IQR_Log2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Efecto</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Sum Sq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mean Sq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NumDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DenDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">F value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pr(&gt;F)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Grupo:Virus</t>
-  </si>
-  <si>
-    <t xml:space="preserve">emmean</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">df</t>
-  </si>
-  <si>
-    <t xml:space="preserve">lower.CL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">upper.CL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">contrast</t>
-  </si>
-  <si>
-    <t xml:space="preserve">estimate</t>
-  </si>
-  <si>
-    <t xml:space="preserve">t.ratio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">p.value</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 µg - 50 µg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 µg - 100 µg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">25 µg - Comm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 µg - 100 µg</t>
-  </si>
-  <si>
-    <t xml:space="preserve">50 µg - Comm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">100 µg - Comm.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B - C</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B - D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">B - E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C - D</t>
-  </si>
-  <si>
-    <t xml:space="preserve">C - E</t>
-  </si>
-  <si>
-    <t xml:space="preserve">D - E</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="500" uniqueCount="84">
+  <si>
+    <t>Section</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Input Data</t>
+  </si>
+  <si>
+    <t>Log2 neutralizing antibody titers dataset</t>
+  </si>
+  <si>
+    <t>Descriptive Stats</t>
+  </si>
+  <si>
+    <t>Summary stats by virus and group (Mean, SD, SEM, Median, IQR)</t>
+  </si>
+  <si>
+    <t>LMM ANOVA</t>
+  </si>
+  <si>
+    <t>Linear Mixed-Effects Model Type III ANOVA table</t>
+  </si>
+  <si>
+    <t>EMMeans</t>
+  </si>
+  <si>
+    <t>Estimated Marginal Means for treatment groups</t>
+  </si>
+  <si>
+    <t>Pairwise Contrasts</t>
+  </si>
+  <si>
+    <t>Pairwise comparisons (BH adjusted p-values)</t>
+  </si>
+  <si>
+    <t>Animal</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Virus</t>
+  </si>
+  <si>
+    <t>Titulo</t>
+  </si>
+  <si>
+    <t>Log2_Titulo</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>Control</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>25 µg</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>50 µg</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>100 µg</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>Comm.</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>Media_Log2</t>
+  </si>
+  <si>
+    <t>SD_Log2</t>
+  </si>
+  <si>
+    <t>SEM_Log2</t>
+  </si>
+  <si>
+    <t>Mediana_Log2</t>
+  </si>
+  <si>
+    <t>IQR_Log2</t>
+  </si>
+  <si>
+    <t>Efecto</t>
+  </si>
+  <si>
+    <t>Sum Sq</t>
+  </si>
+  <si>
+    <t>Mean Sq</t>
+  </si>
+  <si>
+    <t>NumDF</t>
+  </si>
+  <si>
+    <t>DenDF</t>
+  </si>
+  <si>
+    <t>F value</t>
+  </si>
+  <si>
+    <t>Pr(&gt;F)</t>
+  </si>
+  <si>
+    <t>Grupo:Virus</t>
+  </si>
+  <si>
+    <t>emmean</t>
+  </si>
+  <si>
+    <t>SE</t>
+  </si>
+  <si>
+    <t>df</t>
+  </si>
+  <si>
+    <t>lower.CL</t>
+  </si>
+  <si>
+    <t>upper.CL</t>
+  </si>
+  <si>
+    <t>contrast</t>
+  </si>
+  <si>
+    <t>estimate</t>
+  </si>
+  <si>
+    <t>t.ratio</t>
+  </si>
+  <si>
+    <t>p.value</t>
+  </si>
+  <si>
+    <t>25 µg - 50 µg</t>
+  </si>
+  <si>
+    <t>25 µg - 100 µg</t>
+  </si>
+  <si>
+    <t>25 µg - Comm.</t>
+  </si>
+  <si>
+    <t>50 µg - 100 µg</t>
+  </si>
+  <si>
+    <t>50 µg - Comm.</t>
+  </si>
+  <si>
+    <t>100 µg - Comm.</t>
+  </si>
+  <si>
+    <t>B - C</t>
+  </si>
+  <si>
+    <t>B - D</t>
+  </si>
+  <si>
+    <t>B - E</t>
+  </si>
+  <si>
+    <t>C - D</t>
+  </si>
+  <si>
+    <t>C - E</t>
+  </si>
+  <si>
+    <t>D - E</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -313,6 +336,15 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -594,11 +626,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -606,7 +638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>2</v>
       </c>
@@ -614,7 +646,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
@@ -622,7 +654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -630,7 +662,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -638,7 +670,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -648,16 +680,16 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:E93"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>12</v>
       </c>
@@ -674,7 +706,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -684,14 +716,14 @@
       <c r="C2" t="s">
         <v>19</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>5</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>2.32192809488736</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>20</v>
       </c>
@@ -701,14 +733,14 @@
       <c r="C3" t="s">
         <v>19</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>5</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>2.32192809488736</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>21</v>
       </c>
@@ -718,14 +750,14 @@
       <c r="C4" t="s">
         <v>19</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>4060</v>
       </c>
-      <c r="E4" t="n">
-        <v>11.9872640120725</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="E4">
+        <v>11.987264012072499</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>23</v>
       </c>
@@ -735,14 +767,14 @@
       <c r="C5" t="s">
         <v>19</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>10240</v>
       </c>
-      <c r="E5" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>24</v>
       </c>
@@ -752,14 +784,14 @@
       <c r="C6" t="s">
         <v>19</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>6450</v>
       </c>
-      <c r="E6" t="n">
-        <v>12.655083445198</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="E6">
+        <v>12.655083445198001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>25</v>
       </c>
@@ -769,14 +801,14 @@
       <c r="C7" t="s">
         <v>19</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>10240</v>
       </c>
-      <c r="E7" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="E7">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>26</v>
       </c>
@@ -786,14 +818,14 @@
       <c r="C8" t="s">
         <v>19</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>3220</v>
       </c>
-      <c r="E8" t="n">
-        <v>11.652844973002</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="E8">
+        <v>11.652844973002001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -803,14 +835,14 @@
       <c r="C9" t="s">
         <v>19</v>
       </c>
-      <c r="D9" t="n">
+      <c r="D9">
         <v>2560</v>
       </c>
-      <c r="E9" t="n">
-        <v>11.3219280948874</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="E9">
+        <v>11.321928094887401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>28</v>
       </c>
@@ -820,14 +852,14 @@
       <c r="C10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="n">
+      <c r="D10">
         <v>3620</v>
       </c>
-      <c r="E10" t="n">
-        <v>11.8217739819706</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="E10">
+        <v>11.821773981970599</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>29</v>
       </c>
@@ -837,14 +869,14 @@
       <c r="C11" t="s">
         <v>19</v>
       </c>
-      <c r="D11" t="n">
+      <c r="D11">
         <v>20480</v>
       </c>
-      <c r="E11" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="E11">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>31</v>
       </c>
@@ -854,14 +886,14 @@
       <c r="C12" t="s">
         <v>19</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>10240</v>
       </c>
-      <c r="E12" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="E12">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>32</v>
       </c>
@@ -871,14 +903,14 @@
       <c r="C13" t="s">
         <v>19</v>
       </c>
-      <c r="D13" t="n">
+      <c r="D13">
         <v>10240</v>
       </c>
-      <c r="E13" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="E13">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>33</v>
       </c>
@@ -888,14 +920,14 @@
       <c r="C14" t="s">
         <v>19</v>
       </c>
-      <c r="D14" t="n">
+      <c r="D14">
         <v>4060</v>
       </c>
-      <c r="E14" t="n">
-        <v>11.9872640120725</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="E14">
+        <v>11.987264012072499</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>34</v>
       </c>
@@ -905,14 +937,14 @@
       <c r="C15" t="s">
         <v>19</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>20480</v>
       </c>
-      <c r="E15" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="E15">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -922,14 +954,14 @@
       <c r="C16" t="s">
         <v>19</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>10240</v>
       </c>
-      <c r="E16" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="E16">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -939,14 +971,14 @@
       <c r="C17" t="s">
         <v>19</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>3220</v>
       </c>
-      <c r="E17" t="n">
-        <v>11.652844973002</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="E17">
+        <v>11.652844973002001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -956,14 +988,14 @@
       <c r="C18" t="s">
         <v>19</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>3220</v>
       </c>
-      <c r="E18" t="n">
-        <v>11.652844973002</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="E18">
+        <v>11.652844973002001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -973,14 +1005,14 @@
       <c r="C19" t="s">
         <v>19</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>20480</v>
       </c>
-      <c r="E19" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="E19">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -990,14 +1022,14 @@
       <c r="C20" t="s">
         <v>19</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>12900</v>
       </c>
-      <c r="E20" t="n">
-        <v>13.655083445198</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="E20">
+        <v>13.655083445198001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -1007,14 +1039,14 @@
       <c r="C21" t="s">
         <v>19</v>
       </c>
-      <c r="D21" t="n">
+      <c r="D21">
         <v>3220</v>
       </c>
-      <c r="E21" t="n">
-        <v>11.652844973002</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="E21">
+        <v>11.652844973002001</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -1024,14 +1056,14 @@
       <c r="C22" t="s">
         <v>19</v>
       </c>
-      <c r="D22" t="n">
+      <c r="D22">
         <v>20</v>
       </c>
-      <c r="E22" t="n">
+      <c r="E22">
         <v>4.32192809488736</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>44</v>
       </c>
@@ -1041,14 +1073,14 @@
       <c r="C23" t="s">
         <v>19</v>
       </c>
-      <c r="D23" t="n">
+      <c r="D23">
         <v>202</v>
       </c>
-      <c r="E23" t="n">
-        <v>7.65821148275179</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="E23">
+        <v>7.6582114827517902</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>45</v>
       </c>
@@ -1058,14 +1090,14 @@
       <c r="C24" t="s">
         <v>19</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D24">
         <v>57</v>
       </c>
-      <c r="E24" t="n">
-        <v>5.83289001416474</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="E24">
+        <v>5.8328900141647404</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>17</v>
       </c>
@@ -1075,14 +1107,14 @@
       <c r="C25" t="s">
         <v>46</v>
       </c>
-      <c r="D25" t="n">
+      <c r="D25">
         <v>5</v>
       </c>
-      <c r="E25" t="n">
+      <c r="E25">
         <v>2.32192809488736</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>20</v>
       </c>
@@ -1092,14 +1124,14 @@
       <c r="C26" t="s">
         <v>46</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26">
         <v>5</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E26">
         <v>2.32192809488736</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>21</v>
       </c>
@@ -1109,14 +1141,14 @@
       <c r="C27" t="s">
         <v>46</v>
       </c>
-      <c r="D27" t="n">
+      <c r="D27">
         <v>6450</v>
       </c>
-      <c r="E27" t="n">
-        <v>12.655083445198</v>
-      </c>
-    </row>
-    <row r="28">
+      <c r="E27">
+        <v>12.655083445198001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -1126,14 +1158,14 @@
       <c r="C28" t="s">
         <v>46</v>
       </c>
-      <c r="D28" t="n">
+      <c r="D28">
         <v>10240</v>
       </c>
-      <c r="E28" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="29">
+      <c r="E28">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -1143,14 +1175,14 @@
       <c r="C29" t="s">
         <v>46</v>
       </c>
-      <c r="D29" t="n">
+      <c r="D29">
         <v>3620</v>
       </c>
-      <c r="E29" t="n">
-        <v>11.8217739819706</v>
-      </c>
-    </row>
-    <row r="30">
+      <c r="E29">
+        <v>11.821773981970599</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1160,14 +1192,14 @@
       <c r="C30" t="s">
         <v>46</v>
       </c>
-      <c r="D30" t="n">
+      <c r="D30">
         <v>4060</v>
       </c>
-      <c r="E30" t="n">
-        <v>11.9872640120725</v>
-      </c>
-    </row>
-    <row r="31">
+      <c r="E30">
+        <v>11.987264012072499</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1177,14 +1209,14 @@
       <c r="C31" t="s">
         <v>46</v>
       </c>
-      <c r="D31" t="n">
+      <c r="D31">
         <v>1810</v>
       </c>
-      <c r="E31" t="n">
-        <v>10.8217739819706</v>
-      </c>
-    </row>
-    <row r="32">
+      <c r="E31">
+        <v>10.821773981970599</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1194,14 +1226,14 @@
       <c r="C32" t="s">
         <v>46</v>
       </c>
-      <c r="D32" t="n">
+      <c r="D32">
         <v>1610</v>
       </c>
-      <c r="E32" t="n">
-        <v>10.652844973002</v>
-      </c>
-    </row>
-    <row r="33">
+      <c r="E32">
+        <v>10.652844973002001</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1211,14 +1243,14 @@
       <c r="C33" t="s">
         <v>46</v>
       </c>
-      <c r="D33" t="n">
+      <c r="D33">
         <v>3220</v>
       </c>
-      <c r="E33" t="n">
-        <v>11.652844973002</v>
-      </c>
-    </row>
-    <row r="34">
+      <c r="E33">
+        <v>11.652844973002001</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1228,14 +1260,14 @@
       <c r="C34" t="s">
         <v>46</v>
       </c>
-      <c r="D34" t="n">
+      <c r="D34">
         <v>20480</v>
       </c>
-      <c r="E34" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="35">
+      <c r="E34">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>31</v>
       </c>
@@ -1245,14 +1277,14 @@
       <c r="C35" t="s">
         <v>46</v>
       </c>
-      <c r="D35" t="n">
+      <c r="D35">
         <v>10240</v>
       </c>
-      <c r="E35" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="36">
+      <c r="E35">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>32</v>
       </c>
@@ -1262,14 +1294,14 @@
       <c r="C36" t="s">
         <v>46</v>
       </c>
-      <c r="D36" t="n">
+      <c r="D36">
         <v>5020</v>
       </c>
-      <c r="E36" t="n">
+      <c r="E36">
         <v>12.2934716488381</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>33</v>
       </c>
@@ -1279,14 +1311,14 @@
       <c r="C37" t="s">
         <v>46</v>
       </c>
-      <c r="D37" t="n">
+      <c r="D37">
         <v>4060</v>
       </c>
-      <c r="E37" t="n">
-        <v>11.9872640120725</v>
-      </c>
-    </row>
-    <row r="38">
+      <c r="E37">
+        <v>11.987264012072499</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>34</v>
       </c>
@@ -1296,14 +1328,14 @@
       <c r="C38" t="s">
         <v>46</v>
       </c>
-      <c r="D38" t="n">
+      <c r="D38">
         <v>10240</v>
       </c>
-      <c r="E38" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="39">
+      <c r="E38">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>36</v>
       </c>
@@ -1313,14 +1345,14 @@
       <c r="C39" t="s">
         <v>46</v>
       </c>
-      <c r="D39" t="n">
+      <c r="D39">
         <v>20480</v>
       </c>
-      <c r="E39" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="40">
+      <c r="E39">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>37</v>
       </c>
@@ -1330,14 +1362,14 @@
       <c r="C40" t="s">
         <v>46</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D40">
         <v>2560</v>
       </c>
-      <c r="E40" t="n">
-        <v>11.3219280948874</v>
-      </c>
-    </row>
-    <row r="41">
+      <c r="E40">
+        <v>11.321928094887401</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>38</v>
       </c>
@@ -1347,14 +1379,14 @@
       <c r="C41" t="s">
         <v>46</v>
       </c>
-      <c r="D41" t="n">
+      <c r="D41">
         <v>905</v>
       </c>
-      <c r="E41" t="n">
-        <v>9.82177398197057</v>
-      </c>
-    </row>
-    <row r="42">
+      <c r="E41">
+        <v>9.8217739819705692</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>39</v>
       </c>
@@ -1364,14 +1396,14 @@
       <c r="C42" t="s">
         <v>46</v>
       </c>
-      <c r="D42" t="n">
+      <c r="D42">
         <v>5120</v>
       </c>
-      <c r="E42" t="n">
-        <v>12.3219280948874</v>
-      </c>
-    </row>
-    <row r="43">
+      <c r="E42">
+        <v>12.321928094887401</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>40</v>
       </c>
@@ -1381,14 +1413,14 @@
       <c r="C43" t="s">
         <v>46</v>
       </c>
-      <c r="D43" t="n">
+      <c r="D43">
         <v>12900</v>
       </c>
-      <c r="E43" t="n">
-        <v>13.655083445198</v>
-      </c>
-    </row>
-    <row r="44">
+      <c r="E43">
+        <v>13.655083445198001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>41</v>
       </c>
@@ -1398,14 +1430,14 @@
       <c r="C44" t="s">
         <v>46</v>
       </c>
-      <c r="D44" t="n">
+      <c r="D44">
         <v>3620</v>
       </c>
-      <c r="E44" t="n">
-        <v>11.8217739819706</v>
-      </c>
-    </row>
-    <row r="45">
+      <c r="E44">
+        <v>11.821773981970599</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>42</v>
       </c>
@@ -1415,14 +1447,14 @@
       <c r="C45" t="s">
         <v>46</v>
       </c>
-      <c r="D45" t="n">
+      <c r="D45">
         <v>32</v>
       </c>
-      <c r="E45" t="n">
+      <c r="E45">
         <v>5</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -1432,14 +1464,14 @@
       <c r="C46" t="s">
         <v>46</v>
       </c>
-      <c r="D46" t="n">
+      <c r="D46">
         <v>64</v>
       </c>
-      <c r="E46" t="n">
+      <c r="E46">
         <v>6</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>45</v>
       </c>
@@ -1449,14 +1481,14 @@
       <c r="C47" t="s">
         <v>46</v>
       </c>
-      <c r="D47" t="n">
+      <c r="D47">
         <v>64</v>
       </c>
-      <c r="E47" t="n">
+      <c r="E47">
         <v>6</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>17</v>
       </c>
@@ -1466,14 +1498,14 @@
       <c r="C48" t="s">
         <v>47</v>
       </c>
-      <c r="D48" t="n">
+      <c r="D48">
         <v>5</v>
       </c>
-      <c r="E48" t="n">
+      <c r="E48">
         <v>2.32192809488736</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>20</v>
       </c>
@@ -1483,14 +1515,14 @@
       <c r="C49" t="s">
         <v>47</v>
       </c>
-      <c r="D49" t="n">
+      <c r="D49">
         <v>5</v>
       </c>
-      <c r="E49" t="n">
+      <c r="E49">
         <v>2.32192809488736</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>21</v>
       </c>
@@ -1500,14 +1532,14 @@
       <c r="C50" t="s">
         <v>47</v>
       </c>
-      <c r="D50" t="n">
+      <c r="D50">
         <v>6450</v>
       </c>
-      <c r="E50" t="n">
-        <v>12.655083445198</v>
-      </c>
-    </row>
-    <row r="51">
+      <c r="E50">
+        <v>12.655083445198001</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>23</v>
       </c>
@@ -1517,14 +1549,14 @@
       <c r="C51" t="s">
         <v>47</v>
       </c>
-      <c r="D51" t="n">
+      <c r="D51">
         <v>10240</v>
       </c>
-      <c r="E51" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="52">
+      <c r="E51">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>24</v>
       </c>
@@ -1534,14 +1566,14 @@
       <c r="C52" t="s">
         <v>47</v>
       </c>
-      <c r="D52" t="n">
+      <c r="D52">
         <v>10240</v>
       </c>
-      <c r="E52" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="53">
+      <c r="E52">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>25</v>
       </c>
@@ -1551,14 +1583,14 @@
       <c r="C53" t="s">
         <v>47</v>
       </c>
-      <c r="D53" t="n">
+      <c r="D53">
         <v>10240</v>
       </c>
-      <c r="E53" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="54">
+      <c r="E53">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>26</v>
       </c>
@@ -1568,14 +1600,14 @@
       <c r="C54" t="s">
         <v>47</v>
       </c>
-      <c r="D54" t="n">
+      <c r="D54">
         <v>3220</v>
       </c>
-      <c r="E54" t="n">
-        <v>11.652844973002</v>
-      </c>
-    </row>
-    <row r="55">
+      <c r="E54">
+        <v>11.652844973002001</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>27</v>
       </c>
@@ -1585,14 +1617,14 @@
       <c r="C55" t="s">
         <v>47</v>
       </c>
-      <c r="D55" t="n">
+      <c r="D55">
         <v>1020</v>
       </c>
-      <c r="E55" t="n">
-        <v>9.99435343685886</v>
-      </c>
-    </row>
-    <row r="56">
+      <c r="E55">
+        <v>9.9943534368588605</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>28</v>
       </c>
@@ -1602,14 +1634,14 @@
       <c r="C56" t="s">
         <v>47</v>
       </c>
-      <c r="D56" t="n">
+      <c r="D56">
         <v>3220</v>
       </c>
-      <c r="E56" t="n">
-        <v>11.652844973002</v>
-      </c>
-    </row>
-    <row r="57">
+      <c r="E56">
+        <v>11.652844973002001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>29</v>
       </c>
@@ -1619,14 +1651,14 @@
       <c r="C57" t="s">
         <v>47</v>
       </c>
-      <c r="D57" t="n">
+      <c r="D57">
         <v>20480</v>
       </c>
-      <c r="E57" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="58">
+      <c r="E57">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>31</v>
       </c>
@@ -1636,14 +1668,14 @@
       <c r="C58" t="s">
         <v>47</v>
       </c>
-      <c r="D58" t="n">
+      <c r="D58">
         <v>10240</v>
       </c>
-      <c r="E58" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="59">
+      <c r="E58">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>32</v>
       </c>
@@ -1653,14 +1685,14 @@
       <c r="C59" t="s">
         <v>47</v>
       </c>
-      <c r="D59" t="n">
+      <c r="D59">
         <v>4060</v>
       </c>
-      <c r="E59" t="n">
-        <v>11.9872640120725</v>
-      </c>
-    </row>
-    <row r="60">
+      <c r="E59">
+        <v>11.987264012072499</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>33</v>
       </c>
@@ -1670,14 +1702,14 @@
       <c r="C60" t="s">
         <v>47</v>
       </c>
-      <c r="D60" t="n">
+      <c r="D60">
         <v>4060</v>
       </c>
-      <c r="E60" t="n">
-        <v>11.9872640120725</v>
-      </c>
-    </row>
-    <row r="61">
+      <c r="E60">
+        <v>11.987264012072499</v>
+      </c>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>34</v>
       </c>
@@ -1687,14 +1719,14 @@
       <c r="C61" t="s">
         <v>47</v>
       </c>
-      <c r="D61" t="n">
+      <c r="D61">
         <v>20480</v>
       </c>
-      <c r="E61" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="62">
+      <c r="E61">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>36</v>
       </c>
@@ -1704,14 +1736,14 @@
       <c r="C62" t="s">
         <v>47</v>
       </c>
-      <c r="D62" t="n">
+      <c r="D62">
         <v>20480</v>
       </c>
-      <c r="E62" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="63">
+      <c r="E62">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>37</v>
       </c>
@@ -1721,14 +1753,14 @@
       <c r="C63" t="s">
         <v>47</v>
       </c>
-      <c r="D63" t="n">
+      <c r="D63">
         <v>2560</v>
       </c>
-      <c r="E63" t="n">
-        <v>11.3219280948874</v>
-      </c>
-    </row>
-    <row r="64">
+      <c r="E63">
+        <v>11.321928094887401</v>
+      </c>
+    </row>
+    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>38</v>
       </c>
@@ -1738,14 +1770,14 @@
       <c r="C64" t="s">
         <v>47</v>
       </c>
-      <c r="D64" t="n">
+      <c r="D64">
         <v>4060</v>
       </c>
-      <c r="E64" t="n">
-        <v>11.9872640120725</v>
-      </c>
-    </row>
-    <row r="65">
+      <c r="E64">
+        <v>11.987264012072499</v>
+      </c>
+    </row>
+    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>39</v>
       </c>
@@ -1755,14 +1787,14 @@
       <c r="C65" t="s">
         <v>47</v>
       </c>
-      <c r="D65" t="n">
+      <c r="D65">
         <v>20480</v>
       </c>
-      <c r="E65" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="66">
+      <c r="E65">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>40</v>
       </c>
@@ -1772,14 +1804,14 @@
       <c r="C66" t="s">
         <v>47</v>
       </c>
-      <c r="D66" t="n">
+      <c r="D66">
         <v>12900</v>
       </c>
-      <c r="E66" t="n">
-        <v>13.655083445198</v>
-      </c>
-    </row>
-    <row r="67">
+      <c r="E66">
+        <v>13.655083445198001</v>
+      </c>
+    </row>
+    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>41</v>
       </c>
@@ -1789,14 +1821,14 @@
       <c r="C67" t="s">
         <v>47</v>
       </c>
-      <c r="D67" t="n">
+      <c r="D67">
         <v>2030</v>
       </c>
-      <c r="E67" t="n">
-        <v>10.9872640120725</v>
-      </c>
-    </row>
-    <row r="68">
+      <c r="E67">
+        <v>10.987264012072499</v>
+      </c>
+    </row>
+    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>42</v>
       </c>
@@ -1806,14 +1838,14 @@
       <c r="C68" t="s">
         <v>47</v>
       </c>
-      <c r="D68" t="n">
+      <c r="D68">
         <v>127</v>
       </c>
-      <c r="E68" t="n">
-        <v>6.98868468677217</v>
-      </c>
-    </row>
-    <row r="69">
+      <c r="E68">
+        <v>6.9886846867721699</v>
+      </c>
+    </row>
+    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>44</v>
       </c>
@@ -1823,14 +1855,14 @@
       <c r="C69" t="s">
         <v>47</v>
       </c>
-      <c r="D69" t="n">
+      <c r="D69">
         <v>453</v>
       </c>
-      <c r="E69" t="n">
-        <v>8.82336724004623</v>
-      </c>
-    </row>
-    <row r="70">
+      <c r="E69">
+        <v>8.8233672400462293</v>
+      </c>
+    </row>
+    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>45</v>
       </c>
@@ -1840,14 +1872,14 @@
       <c r="C70" t="s">
         <v>47</v>
       </c>
-      <c r="D70" t="n">
+      <c r="D70">
         <v>202</v>
       </c>
-      <c r="E70" t="n">
-        <v>7.65821148275179</v>
-      </c>
-    </row>
-    <row r="71">
+      <c r="E70">
+        <v>7.6582114827517902</v>
+      </c>
+    </row>
+    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>17</v>
       </c>
@@ -1857,14 +1889,14 @@
       <c r="C71" t="s">
         <v>48</v>
       </c>
-      <c r="D71" t="n">
+      <c r="D71">
         <v>5</v>
       </c>
-      <c r="E71" t="n">
+      <c r="E71">
         <v>2.32192809488736</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>20</v>
       </c>
@@ -1874,14 +1906,14 @@
       <c r="C72" t="s">
         <v>48</v>
       </c>
-      <c r="D72" t="n">
+      <c r="D72">
         <v>5</v>
       </c>
-      <c r="E72" t="n">
+      <c r="E72">
         <v>2.32192809488736</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>21</v>
       </c>
@@ -1891,14 +1923,14 @@
       <c r="C73" t="s">
         <v>48</v>
       </c>
-      <c r="D73" t="n">
+      <c r="D73">
         <v>6450</v>
       </c>
-      <c r="E73" t="n">
-        <v>12.655083445198</v>
-      </c>
-    </row>
-    <row r="74">
+      <c r="E73">
+        <v>12.655083445198001</v>
+      </c>
+    </row>
+    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>23</v>
       </c>
@@ -1908,14 +1940,14 @@
       <c r="C74" t="s">
         <v>48</v>
       </c>
-      <c r="D74" t="n">
+      <c r="D74">
         <v>10240</v>
       </c>
-      <c r="E74" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="75">
+      <c r="E74">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>24</v>
       </c>
@@ -1925,14 +1957,14 @@
       <c r="C75" t="s">
         <v>48</v>
       </c>
-      <c r="D75" t="n">
+      <c r="D75">
         <v>6450</v>
       </c>
-      <c r="E75" t="n">
-        <v>12.655083445198</v>
-      </c>
-    </row>
-    <row r="76">
+      <c r="E75">
+        <v>12.655083445198001</v>
+      </c>
+    </row>
+    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>25</v>
       </c>
@@ -1942,14 +1974,14 @@
       <c r="C76" t="s">
         <v>48</v>
       </c>
-      <c r="D76" t="n">
+      <c r="D76">
         <v>6450</v>
       </c>
-      <c r="E76" t="n">
-        <v>12.655083445198</v>
-      </c>
-    </row>
-    <row r="77">
+      <c r="E76">
+        <v>12.655083445198001</v>
+      </c>
+    </row>
+    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>26</v>
       </c>
@@ -1959,14 +1991,14 @@
       <c r="C77" t="s">
         <v>48</v>
       </c>
-      <c r="D77" t="n">
+      <c r="D77">
         <v>3220</v>
       </c>
-      <c r="E77" t="n">
-        <v>11.652844973002</v>
-      </c>
-    </row>
-    <row r="78">
+      <c r="E77">
+        <v>11.652844973002001</v>
+      </c>
+    </row>
+    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>27</v>
       </c>
@@ -1976,14 +2008,14 @@
       <c r="C78" t="s">
         <v>48</v>
       </c>
-      <c r="D78" t="n">
+      <c r="D78">
         <v>1280</v>
       </c>
-      <c r="E78" t="n">
-        <v>10.3219280948874</v>
-      </c>
-    </row>
-    <row r="79">
+      <c r="E78">
+        <v>10.321928094887401</v>
+      </c>
+    </row>
+    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>28</v>
       </c>
@@ -1993,14 +2025,14 @@
       <c r="C79" t="s">
         <v>48</v>
       </c>
-      <c r="D79" t="n">
+      <c r="D79">
         <v>5120</v>
       </c>
-      <c r="E79" t="n">
-        <v>12.3219280948874</v>
-      </c>
-    </row>
-    <row r="80">
+      <c r="E79">
+        <v>12.321928094887401</v>
+      </c>
+    </row>
+    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>29</v>
       </c>
@@ -2010,14 +2042,14 @@
       <c r="C80" t="s">
         <v>48</v>
       </c>
-      <c r="D80" t="n">
+      <c r="D80">
         <v>20480</v>
       </c>
-      <c r="E80" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="81">
+      <c r="E80">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>31</v>
       </c>
@@ -2027,14 +2059,14 @@
       <c r="C81" t="s">
         <v>48</v>
       </c>
-      <c r="D81" t="n">
+      <c r="D81">
         <v>10240</v>
       </c>
-      <c r="E81" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="82">
+      <c r="E81">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>32</v>
       </c>
@@ -2044,14 +2076,14 @@
       <c r="C82" t="s">
         <v>48</v>
       </c>
-      <c r="D82" t="n">
+      <c r="D82">
         <v>5020</v>
       </c>
-      <c r="E82" t="n">
+      <c r="E82">
         <v>12.2934716488381</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>33</v>
       </c>
@@ -2061,14 +2093,14 @@
       <c r="C83" t="s">
         <v>48</v>
       </c>
-      <c r="D83" t="n">
+      <c r="D83">
         <v>2560</v>
       </c>
-      <c r="E83" t="n">
-        <v>11.3219280948874</v>
-      </c>
-    </row>
-    <row r="84">
+      <c r="E83">
+        <v>11.321928094887401</v>
+      </c>
+    </row>
+    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>34</v>
       </c>
@@ -2078,14 +2110,14 @@
       <c r="C84" t="s">
         <v>48</v>
       </c>
-      <c r="D84" t="n">
+      <c r="D84">
         <v>10240</v>
       </c>
-      <c r="E84" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="85">
+      <c r="E84">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>36</v>
       </c>
@@ -2095,14 +2127,14 @@
       <c r="C85" t="s">
         <v>48</v>
       </c>
-      <c r="D85" t="n">
+      <c r="D85">
         <v>10240</v>
       </c>
-      <c r="E85" t="n">
-        <v>13.3219280948874</v>
-      </c>
-    </row>
-    <row r="86">
+      <c r="E85">
+        <v>13.321928094887401</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>37</v>
       </c>
@@ -2112,14 +2144,14 @@
       <c r="C86" t="s">
         <v>48</v>
       </c>
-      <c r="D86" t="n">
+      <c r="D86">
         <v>1610</v>
       </c>
-      <c r="E86" t="n">
-        <v>10.652844973002</v>
-      </c>
-    </row>
-    <row r="87">
+      <c r="E86">
+        <v>10.652844973002001</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>38</v>
       </c>
@@ -2129,14 +2161,14 @@
       <c r="C87" t="s">
         <v>48</v>
       </c>
-      <c r="D87" t="n">
+      <c r="D87">
         <v>2030</v>
       </c>
-      <c r="E87" t="n">
-        <v>10.9872640120725</v>
-      </c>
-    </row>
-    <row r="88">
+      <c r="E87">
+        <v>10.987264012072499</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>39</v>
       </c>
@@ -2146,14 +2178,14 @@
       <c r="C88" t="s">
         <v>48</v>
       </c>
-      <c r="D88" t="n">
+      <c r="D88">
         <v>20480</v>
       </c>
-      <c r="E88" t="n">
-        <v>14.3219280948874</v>
-      </c>
-    </row>
-    <row r="89">
+      <c r="E88">
+        <v>14.321928094887401</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>40</v>
       </c>
@@ -2163,14 +2195,14 @@
       <c r="C89" t="s">
         <v>48</v>
       </c>
-      <c r="D89" t="n">
+      <c r="D89">
         <v>12900</v>
       </c>
-      <c r="E89" t="n">
-        <v>13.655083445198</v>
-      </c>
-    </row>
-    <row r="90">
+      <c r="E89">
+        <v>13.655083445198001</v>
+      </c>
+    </row>
+    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>41</v>
       </c>
@@ -2180,14 +2212,14 @@
       <c r="C90" t="s">
         <v>48</v>
       </c>
-      <c r="D90" t="n">
+      <c r="D90">
         <v>2060</v>
       </c>
-      <c r="E90" t="n">
+      <c r="E90">
         <v>11.0084286220706</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>42</v>
       </c>
@@ -2197,14 +2229,14 @@
       <c r="C91" t="s">
         <v>48</v>
       </c>
-      <c r="D91" t="n">
+      <c r="D91">
         <v>80</v>
       </c>
-      <c r="E91" t="n">
+      <c r="E91">
         <v>6.32192809488736</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>44</v>
       </c>
@@ -2214,14 +2246,14 @@
       <c r="C92" t="s">
         <v>48</v>
       </c>
-      <c r="D92" t="n">
+      <c r="D92">
         <v>320</v>
       </c>
-      <c r="E92" t="n">
+      <c r="E92">
         <v>8.32192809488736</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>45</v>
       </c>
@@ -2231,25 +2263,25 @@
       <c r="C93" t="s">
         <v>48</v>
       </c>
-      <c r="D93" t="n">
+      <c r="D93">
         <v>226</v>
       </c>
-      <c r="E93" t="n">
-        <v>7.82017896241519</v>
+      <c r="E93">
+        <v>7.8201789624151896</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <dimension ref="A1:H21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>14</v>
       </c>
@@ -2275,538 +2307,538 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>19</v>
       </c>
       <c r="B2" t="s">
         <v>18</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>2</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>2.32192809488736</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>2.32192809488736</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>0</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>19</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>7</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>12.2975358138436</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.807945337755462</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.305374633805005</v>
-      </c>
-      <c r="G3" t="n">
-        <v>11.9872640120725</v>
-      </c>
-      <c r="H3" t="n">
+      <c r="E3">
+        <v>0.80794533775546196</v>
+      </c>
+      <c r="F3">
+        <v>0.30537463380500501</v>
+      </c>
+      <c r="G3">
+        <v>11.987264012072499</v>
+      </c>
+      <c r="H3">
         <v>1.2511962925564</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
       <c r="B4" t="s">
         <v>30</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>4</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>13.2382620741837</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.958006298148115</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.479003149074057</v>
       </c>
-      <c r="G4" t="n">
-        <v>13.3219280948874</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0.583666020703706</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="G4">
+        <v>13.321928094887401</v>
+      </c>
+      <c r="H4">
+        <v>0.58366602070370599</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>19</v>
       </c>
       <c r="B5" t="s">
         <v>35</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>7</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>12.9399146641237</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1.25478869813088</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.474265549026971</v>
-      </c>
-      <c r="G5" t="n">
-        <v>13.3219280948874</v>
-      </c>
-      <c r="H5" t="n">
-        <v>2.33566079704069</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="F5">
+        <v>0.47426554902697099</v>
+      </c>
+      <c r="G5">
+        <v>13.321928094887401</v>
+      </c>
+      <c r="H5">
+        <v>2.3356607970406902</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>19</v>
       </c>
       <c r="B6" t="s">
         <v>43</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>3</v>
       </c>
-      <c r="D6" t="n">
-        <v>5.9376765306013</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.67060823401395</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.964526113618362</v>
-      </c>
-      <c r="G6" t="n">
-        <v>5.83289001416474</v>
-      </c>
-      <c r="H6" t="n">
+      <c r="D6">
+        <v>5.9376765306013004</v>
+      </c>
+      <c r="E6">
+        <v>1.6706082340139501</v>
+      </c>
+      <c r="F6">
+        <v>0.96452611361836205</v>
+      </c>
+      <c r="G6">
+        <v>5.8328900141647404</v>
+      </c>
+      <c r="H6">
         <v>1.66814169393222</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>46</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" t="n">
+      <c r="D7">
         <v>2.32192809488736</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>0</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0</v>
       </c>
-      <c r="G7" t="n">
+      <c r="G7">
         <v>2.32192809488736</v>
       </c>
-      <c r="H7" t="n">
+      <c r="H7">
         <v>0</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>46</v>
       </c>
       <c r="B8" t="s">
         <v>22</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>7</v>
       </c>
-      <c r="D8" t="n">
+      <c r="D8">
         <v>11.8447876374433</v>
       </c>
-      <c r="E8" t="n">
-        <v>0.945469778626879</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.357353986624859</v>
-      </c>
-      <c r="G8" t="n">
-        <v>11.8217739819706</v>
-      </c>
-      <c r="H8" t="n">
+      <c r="E8">
+        <v>0.94546977862687898</v>
+      </c>
+      <c r="F8">
+        <v>0.35735398662485901</v>
+      </c>
+      <c r="G8">
+        <v>11.821773981970599</v>
+      </c>
+      <c r="H8">
         <v>1.08386425114898</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>46</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="n">
+      <c r="C9">
         <v>4</v>
       </c>
-      <c r="D9" t="n">
-        <v>12.9811479626713</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D9">
+        <v>12.981147962671299</v>
+      </c>
+      <c r="E9">
         <v>1.06058576288821</v>
       </c>
-      <c r="F9" t="n">
-        <v>0.530292881444104</v>
-      </c>
-      <c r="G9" t="n">
-        <v>12.8076998718627</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="F9">
+        <v>0.53029288144410403</v>
+      </c>
+      <c r="G9">
+        <v>12.807699871862701</v>
+      </c>
+      <c r="H9">
         <v>1.35500835524063</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>46</v>
       </c>
       <c r="B10" t="s">
         <v>35</v>
       </c>
-      <c r="C10" t="n">
+      <c r="C10">
         <v>7</v>
       </c>
-      <c r="D10" t="n">
-        <v>12.3694776840984</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.54177393333271</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="D10">
+        <v>12.369477684098401</v>
+      </c>
+      <c r="E10">
+        <v>1.5417739333327101</v>
+      </c>
+      <c r="F10">
         <v>0.58273577221146</v>
       </c>
-      <c r="G10" t="n">
-        <v>12.3219280948874</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1.91665473161371</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="G10">
+        <v>12.321928094887401</v>
+      </c>
+      <c r="H10">
+        <v>1.9166547316137099</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>46</v>
       </c>
       <c r="B11" t="s">
         <v>43</v>
       </c>
-      <c r="C11" t="n">
+      <c r="C11">
         <v>3</v>
       </c>
-      <c r="D11" t="n">
-        <v>5.66666666666667</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0.577350269189626</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.333333333333333</v>
-      </c>
-      <c r="G11" t="n">
+      <c r="D11">
+        <v>5.6666666666666696</v>
+      </c>
+      <c r="E11">
+        <v>0.57735026918962595</v>
+      </c>
+      <c r="F11">
+        <v>0.33333333333333298</v>
+      </c>
+      <c r="G11">
         <v>6</v>
       </c>
-      <c r="H11" t="n">
+      <c r="H11">
         <v>0.5</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>47</v>
       </c>
       <c r="B12" t="s">
         <v>18</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>2</v>
       </c>
-      <c r="D12" t="n">
+      <c r="D12">
         <v>2.32192809488736</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>0</v>
       </c>
-      <c r="F12" t="n">
+      <c r="F12">
         <v>0</v>
       </c>
-      <c r="G12" t="n">
+      <c r="G12">
         <v>2.32192809488736</v>
       </c>
-      <c r="H12" t="n">
+      <c r="H12">
         <v>0</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>47</v>
       </c>
       <c r="B13" t="s">
         <v>22</v>
       </c>
-      <c r="C13" t="n">
+      <c r="C13">
         <v>7</v>
       </c>
-      <c r="D13" t="n">
-        <v>12.2744158732461</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="D13">
+        <v>12.274415873246101</v>
+      </c>
+      <c r="E13">
         <v>1.25220730749637</v>
       </c>
-      <c r="F13" t="n">
-        <v>0.473289875076169</v>
-      </c>
-      <c r="G13" t="n">
-        <v>12.655083445198</v>
-      </c>
-      <c r="H13" t="n">
-        <v>1.66908312188538</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="F13">
+        <v>0.47328987507616899</v>
+      </c>
+      <c r="G13">
+        <v>12.655083445198001</v>
+      </c>
+      <c r="H13">
+        <v>1.6690831218853801</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>47</v>
       </c>
       <c r="B14" t="s">
         <v>30</v>
       </c>
-      <c r="C14" t="n">
+      <c r="C14">
         <v>4</v>
       </c>
-      <c r="D14" t="n">
-        <v>12.9045960534799</v>
-      </c>
-      <c r="E14" t="n">
+      <c r="D14">
+        <v>12.904596053479899</v>
+      </c>
+      <c r="E14">
         <v>1.13519341916855</v>
       </c>
-      <c r="F14" t="n">
-        <v>0.567596709584276</v>
-      </c>
-      <c r="G14" t="n">
-        <v>12.6545960534799</v>
-      </c>
-      <c r="H14" t="n">
+      <c r="F14">
+        <v>0.56759670958427599</v>
+      </c>
+      <c r="G14">
+        <v>12.654596053479899</v>
+      </c>
+      <c r="H14">
         <v>1.58466408281482</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>47</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>7</v>
       </c>
-      <c r="D15" t="n">
+      <c r="D15">
         <v>12.9881891212704</v>
       </c>
-      <c r="E15" t="n">
+      <c r="E15">
         <v>1.50351284017384</v>
       </c>
-      <c r="F15" t="n">
+      <c r="F15">
         <v>0.568274438298911</v>
       </c>
-      <c r="G15" t="n">
-        <v>13.655083445198</v>
-      </c>
-      <c r="H15" t="n">
+      <c r="G15">
+        <v>13.655083445198001</v>
+      </c>
+      <c r="H15">
         <v>2.66733204140741</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>47</v>
       </c>
       <c r="B16" t="s">
         <v>43</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>3</v>
       </c>
-      <c r="D16" t="n">
-        <v>7.8234211365234</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.928431844615728</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.536030375413112</v>
-      </c>
-      <c r="G16" t="n">
-        <v>7.65821148275179</v>
-      </c>
-      <c r="H16" t="n">
-        <v>0.917341276637035</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="D16">
+        <v>7.8234211365234003</v>
+      </c>
+      <c r="E16">
+        <v>0.92843184461572803</v>
+      </c>
+      <c r="F16">
+        <v>0.53603037541311205</v>
+      </c>
+      <c r="G16">
+        <v>7.6582114827517902</v>
+      </c>
+      <c r="H16">
+        <v>0.91734127663703502</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>48</v>
       </c>
       <c r="B17" t="s">
         <v>18</v>
       </c>
-      <c r="C17" t="n">
+      <c r="C17">
         <v>2</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D17">
         <v>2.32192809488736</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>0</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>0</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G17">
         <v>2.32192809488736</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H17">
         <v>0</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>48</v>
       </c>
       <c r="B18" t="s">
         <v>22</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18">
         <v>7</v>
       </c>
-      <c r="D18" t="n">
+      <c r="D18">
         <v>12.2262685133226</v>
       </c>
-      <c r="E18" t="n">
-        <v>0.976097194400367</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.36893006168732</v>
-      </c>
-      <c r="G18" t="n">
-        <v>12.655083445198</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.667696911253309</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="E18">
+        <v>0.97609719440036702</v>
+      </c>
+      <c r="F18">
+        <v>0.36893006168732001</v>
+      </c>
+      <c r="G18">
+        <v>12.655083445198001</v>
+      </c>
+      <c r="H18">
+        <v>0.66769691125330899</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>48</v>
       </c>
       <c r="B19" t="s">
         <v>30</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>4</v>
       </c>
-      <c r="D19" t="n">
+      <c r="D19">
         <v>12.8148139833751</v>
       </c>
-      <c r="E19" t="n">
-        <v>1.29474112895726</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.647370564478629</v>
-      </c>
-      <c r="G19" t="n">
-        <v>12.8076998718627</v>
-      </c>
-      <c r="H19" t="n">
-        <v>1.52134233453692</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="E19">
+        <v>1.2947411289572599</v>
+      </c>
+      <c r="F19">
+        <v>0.64737056447862895</v>
+      </c>
+      <c r="G19">
+        <v>12.807699871862701</v>
+      </c>
+      <c r="H19">
+        <v>1.5213423345369199</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>48</v>
       </c>
       <c r="B20" t="s">
         <v>35</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>7</v>
       </c>
-      <c r="D20" t="n">
+      <c r="D20">
         <v>12.4670579052865</v>
       </c>
-      <c r="E20" t="n">
-        <v>1.52328111335395</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.575746143253734</v>
-      </c>
-      <c r="G20" t="n">
-        <v>13.3219280948874</v>
-      </c>
-      <c r="H20" t="n">
-        <v>2.49065945297111</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="E20">
+        <v>1.5232811133539499</v>
+      </c>
+      <c r="F20">
+        <v>0.57574614325373397</v>
+      </c>
+      <c r="G20">
+        <v>13.321928094887401</v>
+      </c>
+      <c r="H20">
+        <v>2.4906594529711099</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>48</v>
       </c>
       <c r="B21" t="s">
         <v>43</v>
       </c>
-      <c r="C21" t="n">
+      <c r="C21">
         <v>3</v>
       </c>
-      <c r="D21" t="n">
-        <v>7.48801171739664</v>
-      </c>
-      <c r="E21" t="n">
+      <c r="D21">
+        <v>7.4880117173966401</v>
+      </c>
+      <c r="E21">
         <v>1.04055336672244</v>
       </c>
-      <c r="F21" t="n">
-        <v>0.600763766383373</v>
-      </c>
-      <c r="G21" t="n">
-        <v>7.82017896241519</v>
-      </c>
-      <c r="H21" t="n">
+      <c r="F21">
+        <v>0.60076376638337303</v>
+      </c>
+      <c r="G21">
+        <v>7.8201789624151896</v>
+      </c>
+      <c r="H21">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:G4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>55</v>
       </c>
@@ -2829,87 +2861,87 @@
         <v>61</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>13</v>
       </c>
-      <c r="B2" t="n">
-        <v>17.4645924070669</v>
-      </c>
-      <c r="C2" t="n">
+      <c r="B2">
+        <v>17.464592407066899</v>
+      </c>
+      <c r="C2">
         <v>5.82153080235563</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
-        <v>16.9999938923052</v>
-      </c>
-      <c r="F2" t="n">
-        <v>22.9882045473741</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.00000323886320564675</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2">
+        <v>16.999993892305199</v>
+      </c>
+      <c r="F2">
+        <v>22.988204547374099</v>
+      </c>
+      <c r="G2">
+        <v>3.2388632056467502E-6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3">
         <v>5.91591525727865</v>
       </c>
-      <c r="C3" t="n">
-        <v>1.97197175242622</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>1.9719717524262199</v>
+      </c>
+      <c r="D3">
         <v>3</v>
       </c>
-      <c r="E3" t="n">
-        <v>51.0000021791725</v>
-      </c>
-      <c r="F3" t="n">
-        <v>7.7869707376751</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.0002245257836581</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="E3">
+        <v>51.000002179172498</v>
+      </c>
+      <c r="F3">
+        <v>7.7869707376750998</v>
+      </c>
+      <c r="G3">
+        <v>2.245257836581E-4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>62</v>
       </c>
-      <c r="B4" t="n">
-        <v>9.54404930319679</v>
-      </c>
-      <c r="C4" t="n">
+      <c r="B4">
+        <v>9.5440493031967897</v>
+      </c>
+      <c r="C4">
         <v>1.06044992257742</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>9</v>
       </c>
-      <c r="E4" t="n">
-        <v>51.000002179484</v>
-      </c>
-      <c r="F4" t="n">
-        <v>4.18753083340081</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.000433072465764104</v>
+      <c r="E4">
+        <v>51.000002179483999</v>
+      </c>
+      <c r="F4">
+        <v>4.1875308334008103</v>
+      </c>
+      <c r="G4">
+        <v>4.3307246576410399E-4</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -2932,386 +2964,466 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>22</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>12.2975358138426</v>
       </c>
-      <c r="D2" t="n">
-        <v>0.460089477685205</v>
-      </c>
-      <c r="E2" t="n">
-        <v>22.2062144343669</v>
-      </c>
-      <c r="F2" t="n">
+      <c r="D2">
+        <v>0.46008947768520497</v>
+      </c>
+      <c r="E2">
+        <v>22.206214434366899</v>
+      </c>
+      <c r="F2">
         <v>11.3438821140474</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>13.2511895136377</v>
       </c>
-    </row>
-    <row r="3">
+      <c r="H2">
+        <f>2^C2</f>
+        <v>5034.1616015684231</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>30</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>13.2382620741837</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.608641169396331</v>
-      </c>
-      <c r="E3" t="n">
+      <c r="D3">
+        <v>0.60864116939633095</v>
+      </c>
+      <c r="E3">
         <v>22.2062144343668</v>
       </c>
-      <c r="F3" t="n">
-        <v>11.9766968109164</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="F3">
+        <v>11.976696810916399</v>
+      </c>
+      <c r="G3">
         <v>14.499827337451</v>
       </c>
-    </row>
-    <row r="4">
+      <c r="H3">
+        <f t="shared" ref="H3:H17" si="0">2^C3</f>
+        <v>9663.0443941926151</v>
+      </c>
+      <c r="I3">
+        <f>MAX(H2:H4,H6:H8,H10:H12,H14:H16)</f>
+        <v>9663.0443941926151</v>
+      </c>
+      <c r="J3">
+        <f>MIN(H2:H4,H6:H8,H10:H12,H14:H16)</f>
+        <v>3678.2087326445144</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>35</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="n">
-        <v>12.9399146641239</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.460089477685208</v>
-      </c>
-      <c r="E4" t="n">
-        <v>22.2062144343669</v>
-      </c>
-      <c r="F4" t="n">
+      <c r="C4">
+        <v>12.939914664123901</v>
+      </c>
+      <c r="D4">
+        <v>0.46008947768520803</v>
+      </c>
+      <c r="E4">
+        <v>22.206214434366899</v>
+      </c>
+      <c r="F4">
         <v>11.9862609643287</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>13.893568363919</v>
       </c>
-    </row>
-    <row r="5">
+      <c r="H4">
+        <f t="shared" si="0"/>
+        <v>7857.8268587776856</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>43</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="n">
-        <v>5.93767653060132</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>5.9376765306013199</v>
+      </c>
+      <c r="D5">
         <v>0.702798285981721</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>22.2062144343668</v>
       </c>
-      <c r="F5" t="n">
-        <v>4.480946441906</v>
-      </c>
-      <c r="G5" t="n">
-        <v>7.39440661929664</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="F5">
+        <v>4.4809464419060001</v>
+      </c>
+      <c r="G5">
+        <v>7.3944066192966398</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="0"/>
+        <v>61.29410955661379</v>
+      </c>
+      <c r="I5">
+        <f>MAX(H5,H9,H13,H17)</f>
+        <v>226.50846178836343</v>
+      </c>
+      <c r="J5">
+        <f>MIN(H5,H9,H13,H17)</f>
+        <v>50.796833662982856</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>22</v>
       </c>
       <c r="B6" t="s">
         <v>46</v>
       </c>
-      <c r="C6" t="n">
-        <v>11.8447876374425</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.460089477685206</v>
-      </c>
-      <c r="E6" t="n">
-        <v>22.2062144343675</v>
-      </c>
-      <c r="F6" t="n">
+      <c r="C6">
+        <v>11.844787637442501</v>
+      </c>
+      <c r="D6">
+        <v>0.46008947768520603</v>
+      </c>
+      <c r="E6">
+        <v>22.206214434367499</v>
+      </c>
+      <c r="F6">
         <v>10.8911339376473</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>12.7984413372376</v>
       </c>
-    </row>
-    <row r="7">
+      <c r="H6">
+        <f t="shared" si="0"/>
+        <v>3678.2087326445144</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>30</v>
       </c>
       <c r="B7" t="s">
         <v>46</v>
       </c>
-      <c r="C7" t="n">
+      <c r="C7">
         <v>12.9811479626714</v>
       </c>
-      <c r="D7" t="n">
-        <v>0.608641169396331</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="D7">
+        <v>0.60864116939633095</v>
+      </c>
+      <c r="E7">
         <v>22.2062144343668</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>11.7195826994041</v>
       </c>
-      <c r="G7" t="n">
-        <v>14.2427132259387</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="G7">
+        <v>14.242713225938701</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="0"/>
+        <v>8085.6495648532837</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>35</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" t="n">
+      <c r="C8">
         <v>12.3694776840985</v>
       </c>
-      <c r="D8" t="n">
-        <v>0.460089477685208</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="D8">
+        <v>0.46008947768520803</v>
+      </c>
+      <c r="E8">
         <v>22.2062144343668</v>
       </c>
-      <c r="F8" t="n">
+      <c r="F8">
         <v>11.4158239843033</v>
       </c>
-      <c r="G8" t="n">
+      <c r="G8">
         <v>13.3231313838936</v>
       </c>
-    </row>
-    <row r="9">
+      <c r="H8">
+        <f t="shared" si="0"/>
+        <v>5291.5610811861206</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>43</v>
       </c>
       <c r="B9" t="s">
         <v>46</v>
       </c>
-      <c r="C9" t="n">
-        <v>5.66666666666668</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C9">
+        <v>5.6666666666666803</v>
+      </c>
+      <c r="D9">
         <v>0.702798285981721</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E9">
         <v>22.2062144343668</v>
       </c>
-      <c r="F9" t="n">
-        <v>4.20993657797136</v>
-      </c>
-      <c r="G9" t="n">
-        <v>7.123396755362</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="F9">
+        <v>4.2099365779713596</v>
+      </c>
+      <c r="G9">
+        <v>7.1233967553620001</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="0"/>
+        <v>50.796833662982856</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>22</v>
       </c>
       <c r="B10" t="s">
         <v>47</v>
       </c>
-      <c r="C10" t="n">
-        <v>12.2744158732453</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.460089477685206</v>
-      </c>
-      <c r="E10" t="n">
-        <v>22.2062144343675</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="C10">
+        <v>12.274415873245299</v>
+      </c>
+      <c r="D10">
+        <v>0.46008947768520603</v>
+      </c>
+      <c r="E10">
+        <v>22.206214434367499</v>
+      </c>
+      <c r="F10">
         <v>11.3207621734502</v>
       </c>
-      <c r="G10" t="n">
-        <v>13.2280695730404</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="G10">
+        <v>13.228069573040401</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="0"/>
+        <v>4954.1295265543258</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>30</v>
       </c>
       <c r="B11" t="s">
         <v>47</v>
       </c>
-      <c r="C11" t="n">
-        <v>12.90459605348</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.608641169396331</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="C11">
+        <v>12.904596053480001</v>
+      </c>
+      <c r="D11">
+        <v>0.60864116939633095</v>
+      </c>
+      <c r="E11">
         <v>22.2062144343668</v>
       </c>
-      <c r="F11" t="n">
+      <c r="F11">
         <v>11.6430307902127</v>
       </c>
-      <c r="G11" t="n">
-        <v>14.1661613167473</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="G11">
+        <v>14.166161316747299</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="0"/>
+        <v>7667.7950107920888</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>35</v>
       </c>
       <c r="B12" t="s">
         <v>47</v>
       </c>
-      <c r="C12" t="n">
+      <c r="C12">
         <v>12.9881891212705</v>
       </c>
-      <c r="D12" t="n">
-        <v>0.460089477685208</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="D12">
+        <v>0.46008947768520803</v>
+      </c>
+      <c r="E12">
         <v>22.2062144343668</v>
       </c>
-      <c r="F12" t="n">
-        <v>12.0345354214753</v>
-      </c>
-      <c r="G12" t="n">
-        <v>13.9418428210656</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="F12">
+        <v>12.034535421475301</v>
+      </c>
+      <c r="G12">
+        <v>13.941842821065601</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="0"/>
+        <v>8125.2085128447525</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>43</v>
       </c>
       <c r="B13" t="s">
         <v>47</v>
       </c>
-      <c r="C13" t="n">
-        <v>7.82342113652341</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13">
+        <v>7.8234211365234101</v>
+      </c>
+      <c r="D13">
         <v>0.702798285981721</v>
       </c>
-      <c r="E13" t="n">
+      <c r="E13">
         <v>22.2062144343668</v>
       </c>
-      <c r="F13" t="n">
-        <v>6.36669104782809</v>
-      </c>
-      <c r="G13" t="n">
-        <v>9.28015122521873</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="F13">
+        <v>6.3666910478280903</v>
+      </c>
+      <c r="G13">
+        <v>9.2801512252187308</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="0"/>
+        <v>226.50846178836343</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>22</v>
       </c>
       <c r="B14" t="s">
         <v>48</v>
       </c>
-      <c r="C14" t="n">
-        <v>12.2262685133217</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.460089477685206</v>
-      </c>
-      <c r="E14" t="n">
-        <v>22.2062144343676</v>
-      </c>
-      <c r="F14" t="n">
+      <c r="C14">
+        <v>12.226268513321701</v>
+      </c>
+      <c r="D14">
+        <v>0.46008947768520603</v>
+      </c>
+      <c r="E14">
+        <v>22.206214434367599</v>
+      </c>
+      <c r="F14">
         <v>11.2726148135266</v>
       </c>
-      <c r="G14" t="n">
+      <c r="G14">
         <v>13.1799222131169</v>
       </c>
-    </row>
-    <row r="15">
+      <c r="H14">
+        <f t="shared" si="0"/>
+        <v>4791.5227836076947</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>30</v>
       </c>
       <c r="B15" t="s">
         <v>48</v>
       </c>
-      <c r="C15" t="n">
+      <c r="C15">
         <v>12.8148139833751</v>
       </c>
-      <c r="D15" t="n">
-        <v>0.608641169396331</v>
-      </c>
-      <c r="E15" t="n">
+      <c r="D15">
+        <v>0.60864116939633095</v>
+      </c>
+      <c r="E15">
         <v>22.2062144343668</v>
       </c>
-      <c r="F15" t="n">
-        <v>11.5532487201078</v>
-      </c>
-      <c r="G15" t="n">
+      <c r="F15">
+        <v>11.553248720107799</v>
+      </c>
+      <c r="G15">
         <v>14.0763792466424</v>
       </c>
-    </row>
-    <row r="16">
+      <c r="H15">
+        <f t="shared" si="0"/>
+        <v>7205.1561595694993</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>35</v>
       </c>
       <c r="B16" t="s">
         <v>48</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>12.4670579052866</v>
       </c>
-      <c r="D16" t="n">
-        <v>0.460089477685208</v>
-      </c>
-      <c r="E16" t="n">
+      <c r="D16">
+        <v>0.46008947768520803</v>
+      </c>
+      <c r="E16">
         <v>22.2062144343668</v>
       </c>
-      <c r="F16" t="n">
-        <v>11.5134042054914</v>
-      </c>
-      <c r="G16" t="n">
-        <v>13.4207116050817</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="F16">
+        <v>11.513404205491399</v>
+      </c>
+      <c r="G16">
+        <v>13.420711605081699</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="0"/>
+        <v>5661.850362423972</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>43</v>
       </c>
       <c r="B17" t="s">
         <v>48</v>
       </c>
-      <c r="C17" t="n">
-        <v>7.48801171739665</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17">
+        <v>7.4880117173966498</v>
+      </c>
+      <c r="D17">
         <v>0.702798285981721</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>22.2062144343668</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>6.03128162870133</v>
       </c>
-      <c r="G17" t="n">
-        <v>8.94474180609197</v>
+      <c r="G17">
+        <v>8.9447418060919706</v>
+      </c>
+      <c r="H17">
+        <f t="shared" si="0"/>
+        <v>179.521362127348</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>68</v>
       </c>
@@ -3334,570 +3446,570 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>72</v>
       </c>
       <c r="B2" t="s">
         <v>19</v>
       </c>
-      <c r="C2" t="n">
-        <v>-0.940726260341108</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.762972083736213</v>
-      </c>
-      <c r="E2" t="n">
+      <c r="C2">
+        <v>-0.94072626034110796</v>
+      </c>
+      <c r="D2">
+        <v>0.76297208373621295</v>
+      </c>
+      <c r="E2">
         <v>22.2062144343668</v>
       </c>
-      <c r="F2" t="n">
-        <v>-1.23297599007089</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="F2">
+        <v>-1.2329759900708901</v>
+      </c>
+      <c r="G2">
         <v>0.345717674955137</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
       <c r="B3" t="s">
         <v>19</v>
       </c>
-      <c r="C3" t="n">
-        <v>-0.642378850281292</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.650664779247573</v>
-      </c>
-      <c r="E3" t="n">
-        <v>22.2062144343669</v>
-      </c>
-      <c r="F3" t="n">
-        <v>-0.987265441083406</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.400978121168337</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3">
+        <v>-0.64237885028129205</v>
+      </c>
+      <c r="D3">
+        <v>0.65066477924757304</v>
+      </c>
+      <c r="E3">
+        <v>22.206214434366899</v>
+      </c>
+      <c r="F3">
+        <v>-0.98726544108340597</v>
+      </c>
+      <c r="G3">
+        <v>0.40097812116833698</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>74</v>
       </c>
       <c r="B4" t="s">
         <v>19</v>
       </c>
-      <c r="C4" t="n">
-        <v>6.35985928324126</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.840004617996526</v>
-      </c>
-      <c r="E4" t="n">
-        <v>22.2062144343669</v>
-      </c>
-      <c r="F4" t="n">
-        <v>7.57121942782886</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.000000273846942666379</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4">
+        <v>6.3598592832412599</v>
+      </c>
+      <c r="D4">
+        <v>0.84000461799652604</v>
+      </c>
+      <c r="E4">
+        <v>22.206214434366899</v>
+      </c>
+      <c r="F4">
+        <v>7.5712194278288596</v>
+      </c>
+      <c r="G4">
+        <v>2.7384694266637898E-7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>75</v>
       </c>
       <c r="B5" t="s">
         <v>19</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.298347410059816</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.762972083736215</v>
-      </c>
-      <c r="E5" t="n">
+      <c r="C5">
+        <v>0.29834741005981602</v>
+      </c>
+      <c r="D5">
+        <v>0.76297208373621495</v>
+      </c>
+      <c r="E5">
         <v>22.2062144343668</v>
       </c>
-      <c r="F5" t="n">
-        <v>0.391033192982411</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.699499293365547</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="F5">
+        <v>0.39103319298241102</v>
+      </c>
+      <c r="G5">
+        <v>0.69949929336554695</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>76</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
-      <c r="C6" t="n">
-        <v>7.30058554358236</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>7.3005855435823603</v>
+      </c>
+      <c r="D6">
         <v>0.929714743275042</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>22.2062144343668</v>
       </c>
-      <c r="F6" t="n">
-        <v>7.85250056147877</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.000000225749861495315</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="F6">
+        <v>7.8525005614787702</v>
+      </c>
+      <c r="G6">
+        <v>2.25749861495315E-7</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>77</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
-      <c r="C7" t="n">
-        <v>7.00223813352255</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.840004617996528</v>
-      </c>
-      <c r="E7" t="n">
+      <c r="C7">
+        <v>7.0022381335225496</v>
+      </c>
+      <c r="D7">
+        <v>0.84000461799652804</v>
+      </c>
+      <c r="E7">
         <v>22.2062144343668</v>
       </c>
-      <c r="F7" t="n">
-        <v>8.33595195014927</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.000000165411276271597</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="F7">
+        <v>8.3359519501492692</v>
+      </c>
+      <c r="G7">
+        <v>1.6541127627159701E-7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>72</v>
       </c>
       <c r="B8" t="s">
         <v>46</v>
       </c>
-      <c r="C8" t="n">
-        <v>-1.13636032522891</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.762972083736213</v>
-      </c>
-      <c r="E8" t="n">
-        <v>22.2062144343671</v>
-      </c>
-      <c r="F8" t="n">
+      <c r="C8">
+        <v>-1.1363603252289101</v>
+      </c>
+      <c r="D8">
+        <v>0.76297208373621295</v>
+      </c>
+      <c r="E8">
+        <v>22.206214434367102</v>
+      </c>
+      <c r="F8">
         <v>-1.48938650502682</v>
       </c>
-      <c r="G8" t="n">
-        <v>0.225678252888539</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="G8">
+        <v>0.22567825288853899</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>73</v>
       </c>
       <c r="B9" t="s">
         <v>46</v>
       </c>
-      <c r="C9" t="n">
-        <v>-0.524690046656028</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.650664779247573</v>
-      </c>
-      <c r="E9" t="n">
-        <v>22.2062144343672</v>
-      </c>
-      <c r="F9" t="n">
-        <v>-0.806390730512228</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.431225643420854</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="C9">
+        <v>-0.52469004665602803</v>
+      </c>
+      <c r="D9">
+        <v>0.65066477924757304</v>
+      </c>
+      <c r="E9">
+        <v>22.206214434367201</v>
+      </c>
+      <c r="F9">
+        <v>-0.80639073051222798</v>
+      </c>
+      <c r="G9">
+        <v>0.43122564342085401</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>74</v>
       </c>
       <c r="B10" t="s">
         <v>46</v>
       </c>
-      <c r="C10" t="n">
-        <v>6.17812097077578</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.840004617996526</v>
-      </c>
-      <c r="E10" t="n">
-        <v>22.206214434367</v>
-      </c>
-      <c r="F10" t="n">
-        <v>7.35486548337205</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.000000437115681132769</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10">
+        <v>6.1781209707757796</v>
+      </c>
+      <c r="D10">
+        <v>0.84000461799652604</v>
+      </c>
+      <c r="E10">
+        <v>22.206214434366998</v>
+      </c>
+      <c r="F10">
+        <v>7.3548654833720502</v>
+      </c>
+      <c r="G10">
+        <v>4.3711568113276902E-7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>75</v>
       </c>
       <c r="B11" t="s">
         <v>46</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.611670278572883</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.762972083736215</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="C11">
+        <v>0.61167027857288303</v>
+      </c>
+      <c r="D11">
+        <v>0.76297208373621495</v>
+      </c>
+      <c r="E11">
         <v>22.2062144343668</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.801694179395898</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.431225643420854</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="F11">
+        <v>0.80169417939589804</v>
+      </c>
+      <c r="G11">
+        <v>0.43122564342085401</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>76</v>
       </c>
       <c r="B12" t="s">
         <v>46</v>
       </c>
-      <c r="C12" t="n">
-        <v>7.31448129600469</v>
-      </c>
-      <c r="D12" t="n">
+      <c r="C12">
+        <v>7.3144812960046899</v>
+      </c>
+      <c r="D12">
         <v>0.929714743275043</v>
       </c>
-      <c r="E12" t="n">
+      <c r="E12">
         <v>22.2062144343668</v>
       </c>
-      <c r="F12" t="n">
-        <v>7.86744681517953</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.000000218747074588393</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="F12">
+        <v>7.8674468151795303</v>
+      </c>
+      <c r="G12">
+        <v>2.18747074588393E-7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>77</v>
       </c>
       <c r="B13" t="s">
         <v>46</v>
       </c>
-      <c r="C13" t="n">
-        <v>6.70281101743181</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.840004617996528</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="C13">
+        <v>6.7028110174318103</v>
+      </c>
+      <c r="D13">
+        <v>0.84000461799652804</v>
+      </c>
+      <c r="E13">
         <v>22.2062144343668</v>
       </c>
-      <c r="F13" t="n">
-        <v>7.97949305733402</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.000000218747074588393</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="F13">
+        <v>7.9794930573340199</v>
+      </c>
+      <c r="G13">
+        <v>2.18747074588393E-7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>72</v>
       </c>
       <c r="B14" t="s">
         <v>47</v>
       </c>
-      <c r="C14" t="n">
-        <v>-0.630180180234673</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.762972083736213</v>
-      </c>
-      <c r="E14" t="n">
-        <v>22.206214434367</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.825954440100523</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.501139177738202</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="C14">
+        <v>-0.63018018023467304</v>
+      </c>
+      <c r="D14">
+        <v>0.76297208373621295</v>
+      </c>
+      <c r="E14">
+        <v>22.206214434366998</v>
+      </c>
+      <c r="F14">
+        <v>-0.82595444010052299</v>
+      </c>
+      <c r="G14">
+        <v>0.50113917773820205</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>73</v>
       </c>
       <c r="B15" t="s">
         <v>47</v>
       </c>
-      <c r="C15" t="n">
-        <v>-0.713773248025181</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.650664779247573</v>
-      </c>
-      <c r="E15" t="n">
-        <v>22.2062144343671</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-1.09699075590135</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.426598952433548</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C15">
+        <v>-0.71377324802518105</v>
+      </c>
+      <c r="D15">
+        <v>0.65066477924757304</v>
+      </c>
+      <c r="E15">
+        <v>22.206214434367102</v>
+      </c>
+      <c r="F15">
+        <v>-1.0969907559013501</v>
+      </c>
+      <c r="G15">
+        <v>0.42659895243354801</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>74</v>
       </c>
       <c r="B16" t="s">
         <v>47</v>
       </c>
-      <c r="C16" t="n">
-        <v>4.45099473672188</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.840004617996526</v>
-      </c>
-      <c r="E16" t="n">
-        <v>22.2062144343671</v>
-      </c>
-      <c r="F16" t="n">
-        <v>5.29877412738258</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.0000497841120765172</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="C16">
+        <v>4.4509947367218796</v>
+      </c>
+      <c r="D16">
+        <v>0.84000461799652604</v>
+      </c>
+      <c r="E16">
+        <v>22.206214434367102</v>
+      </c>
+      <c r="F16">
+        <v>5.2987741273825799</v>
+      </c>
+      <c r="G16">
+        <v>4.9784112076517198E-5</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>75</v>
       </c>
       <c r="B17" t="s">
         <v>47</v>
       </c>
-      <c r="C17" t="n">
-        <v>-0.0835930677905083</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.762972083736215</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="C17">
+        <v>-8.3593067790508305E-2</v>
+      </c>
+      <c r="D17">
+        <v>0.76297208373621495</v>
+      </c>
+      <c r="E17">
         <v>22.2062144343668</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F17">
         <v>-0.109562419874079</v>
       </c>
-      <c r="G17" t="n">
-        <v>0.913740507962407</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="G17">
+        <v>0.91374050796240702</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>76</v>
       </c>
       <c r="B18" t="s">
         <v>47</v>
       </c>
-      <c r="C18" t="n">
-        <v>5.08117491695656</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="C18">
+        <v>5.0811749169565603</v>
+      </c>
+      <c r="D18">
         <v>0.929714743275043</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>22.2062144343668</v>
       </c>
-      <c r="F18" t="n">
-        <v>5.4653053032777</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.0000497841120765172</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="F18">
+        <v>5.4653053032776997</v>
+      </c>
+      <c r="G18">
+        <v>4.9784112076517198E-5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>77</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="n">
+      <c r="C19">
         <v>5.16476798474707</v>
       </c>
-      <c r="D19" t="n">
-        <v>0.840004617996528</v>
-      </c>
-      <c r="E19" t="n">
-        <v>22.2062144343669</v>
-      </c>
-      <c r="F19" t="n">
-        <v>6.14849951309246</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.0000198848678044719</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="D19">
+        <v>0.84000461799652804</v>
+      </c>
+      <c r="E19">
+        <v>22.206214434366899</v>
+      </c>
+      <c r="F19">
+        <v>6.1484995130924602</v>
+      </c>
+      <c r="G19">
+        <v>1.9884867804471899E-5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>72</v>
       </c>
       <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="n">
-        <v>-0.58854547005333</v>
-      </c>
-      <c r="D20" t="n">
-        <v>0.762972083736213</v>
-      </c>
-      <c r="E20" t="n">
-        <v>22.2062144343671</v>
-      </c>
-      <c r="F20" t="n">
-        <v>-0.771385326670498</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.672914478144461</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="C20">
+        <v>-0.58854547005333002</v>
+      </c>
+      <c r="D20">
+        <v>0.76297208373621295</v>
+      </c>
+      <c r="E20">
+        <v>22.206214434367102</v>
+      </c>
+      <c r="F20">
+        <v>-0.77138532667049797</v>
+      </c>
+      <c r="G20">
+        <v>0.67291447814446104</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>73</v>
       </c>
       <c r="B21" t="s">
         <v>48</v>
       </c>
-      <c r="C21" t="n">
-        <v>-0.240789391964826</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.650664779247573</v>
-      </c>
-      <c r="E21" t="n">
-        <v>22.2062144343672</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-0.370066737350182</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.71483889778</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="C21">
+        <v>-0.24078939196482599</v>
+      </c>
+      <c r="D21">
+        <v>0.65066477924757304</v>
+      </c>
+      <c r="E21">
+        <v>22.206214434367201</v>
+      </c>
+      <c r="F21">
+        <v>-0.37006673735018197</v>
+      </c>
+      <c r="G21">
+        <v>0.71483889777999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>74</v>
       </c>
       <c r="B22" t="s">
         <v>48</v>
       </c>
-      <c r="C22" t="n">
-        <v>4.7382567959251</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.840004617996527</v>
-      </c>
-      <c r="E22" t="n">
-        <v>22.206214434367</v>
-      </c>
-      <c r="F22" t="n">
-        <v>5.64075088923462</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.0000219252937702422</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22">
+        <v>4.7382567959250999</v>
+      </c>
+      <c r="D22">
+        <v>0.84000461799652704</v>
+      </c>
+      <c r="E22">
+        <v>22.206214434366998</v>
+      </c>
+      <c r="F22">
+        <v>5.6407508892346199</v>
+      </c>
+      <c r="G22">
+        <v>2.19252937702422E-5</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>75</v>
       </c>
       <c r="B23" t="s">
         <v>48</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.347756078088503</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.762972083736215</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="C23">
+        <v>0.34775607808850301</v>
+      </c>
+      <c r="D23">
+        <v>0.76297208373621495</v>
+      </c>
+      <c r="E23">
         <v>22.2062144343668</v>
       </c>
-      <c r="F23" t="n">
-        <v>0.455791352660728</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.71483889778</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="F23">
+        <v>0.45579135266072801</v>
+      </c>
+      <c r="G23">
+        <v>0.71483889777999998</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>76</v>
       </c>
       <c r="B24" t="s">
         <v>48</v>
       </c>
-      <c r="C24" t="n">
-        <v>5.32680226597842</v>
-      </c>
-      <c r="D24" t="n">
+      <c r="C24">
+        <v>5.3268022659784204</v>
+      </c>
+      <c r="D24">
         <v>0.929714743275043</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E24">
         <v>22.2062144343668</v>
       </c>
-      <c r="F24" t="n">
-        <v>5.72950176869742</v>
-      </c>
-      <c r="G24" t="n">
-        <v>0.0000219252937702422</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="F24">
+        <v>5.7295017686974203</v>
+      </c>
+      <c r="G24">
+        <v>2.19252937702422E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>77</v>
       </c>
       <c r="B25" t="s">
         <v>48</v>
       </c>
-      <c r="C25" t="n">
-        <v>4.97904618788992</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.840004617996528</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="C25">
+        <v>4.9790461878899199</v>
+      </c>
+      <c r="D25">
+        <v>0.84000461799652804</v>
+      </c>
+      <c r="E25">
         <v>22.2062144343668</v>
       </c>
-      <c r="F25" t="n">
-        <v>5.92740335138313</v>
-      </c>
-      <c r="G25" t="n">
-        <v>0.0000219252937702422</v>
+      <c r="F25">
+        <v>5.9274033513831297</v>
+      </c>
+      <c r="G25">
+        <v>2.19252937702422E-5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+  <dimension ref="A1:G25"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>68</v>
       </c>
@@ -3920,560 +4032,560 @@
         <v>71</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>78</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.452748176400114</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.268987470711748</v>
       </c>
-      <c r="E2" t="n">
-        <v>50.9999999999994</v>
-      </c>
-      <c r="F2" t="n">
-        <v>1.68315711955702</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0.324422253632744</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="E2">
+        <v>50.999999999999403</v>
+      </c>
+      <c r="F2">
+        <v>1.6831571195570201</v>
+      </c>
+      <c r="G2">
+        <v>0.32442225363274402</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>79</v>
       </c>
       <c r="B3" t="s">
         <v>22</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.0231199405972752</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C3">
+        <v>2.31199405972752E-2</v>
+      </c>
+      <c r="D3">
         <v>0.268987470711748</v>
       </c>
-      <c r="E3" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.0859517379605048</v>
-      </c>
-      <c r="G3" t="n">
-        <v>0.931841340786635</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="E3">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F3">
+        <v>8.5951737960504801E-2</v>
+      </c>
+      <c r="G3">
+        <v>0.93184134078663505</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>80</v>
       </c>
       <c r="B4" t="s">
         <v>22</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.0712673005208258</v>
-      </c>
-      <c r="D4" t="n">
+      <c r="C4">
+        <v>7.1267300520825805E-2</v>
+      </c>
+      <c r="D4">
         <v>0.268987470711749</v>
       </c>
-      <c r="E4" t="n">
-        <v>51.0000000000003</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.264946543168909</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0.931841340786635</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="E4">
+        <v>51.000000000000298</v>
+      </c>
+      <c r="F4">
+        <v>0.26494654316890898</v>
+      </c>
+      <c r="G4">
+        <v>0.93184134078663505</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>81</v>
       </c>
       <c r="B5" t="s">
         <v>22</v>
       </c>
-      <c r="C5" t="n">
-        <v>-0.429628235802839</v>
-      </c>
-      <c r="D5" t="n">
+      <c r="C5">
+        <v>-0.42962823580283899</v>
+      </c>
+      <c r="D5">
         <v>0.268987470711748</v>
       </c>
-      <c r="E5" t="n">
-        <v>50.9999999999995</v>
-      </c>
-      <c r="F5" t="n">
-        <v>-1.59720538159651</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0.324422253632744</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="E5">
+        <v>50.999999999999503</v>
+      </c>
+      <c r="F5">
+        <v>-1.5972053815965099</v>
+      </c>
+      <c r="G5">
+        <v>0.32442225363274402</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>82</v>
       </c>
       <c r="B6" t="s">
         <v>22</v>
       </c>
-      <c r="C6" t="n">
-        <v>-0.381480875879288</v>
-      </c>
-      <c r="D6" t="n">
+      <c r="C6">
+        <v>-0.38148087587928797</v>
+      </c>
+      <c r="D6">
         <v>0.268987470711748</v>
       </c>
-      <c r="E6" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F6" t="n">
-        <v>-1.41821057638811</v>
-      </c>
-      <c r="G6" t="n">
-        <v>0.324422253632744</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="E6">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F6">
+        <v>-1.4182105763881101</v>
+      </c>
+      <c r="G6">
+        <v>0.32442225363274402</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>83</v>
       </c>
       <c r="B7" t="s">
         <v>22</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.0481473599235507</v>
-      </c>
-      <c r="D7" t="n">
+      <c r="C7">
+        <v>4.8147359923550702E-2</v>
+      </c>
+      <c r="D7">
         <v>0.268987470711748</v>
       </c>
-      <c r="E7" t="n">
+      <c r="E7">
         <v>51</v>
       </c>
-      <c r="F7" t="n">
+      <c r="F7">
         <v>0.178994805208404</v>
       </c>
-      <c r="G7" t="n">
-        <v>0.931841340786635</v>
-      </c>
-    </row>
-    <row r="8">
+      <c r="G7">
+        <v>0.93184134078663505</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>78</v>
       </c>
       <c r="B8" t="s">
         <v>30</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.25711411151231</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.355836976647779</v>
-      </c>
-      <c r="E8" t="n">
+      <c r="C8">
+        <v>0.25711411151231001</v>
+      </c>
+      <c r="D8">
+        <v>0.35583697664777902</v>
+      </c>
+      <c r="E8">
         <v>51</v>
       </c>
-      <c r="F8" t="n">
-        <v>0.72256153347102</v>
-      </c>
-      <c r="G8" t="n">
-        <v>0.830522428235723</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="F8">
+        <v>0.72256153347102003</v>
+      </c>
+      <c r="G8">
+        <v>0.83052242823572298</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>79</v>
       </c>
       <c r="B9" t="s">
         <v>30</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.33366602070371</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.355836976647778</v>
-      </c>
-      <c r="E9" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.937693501802612</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.830522428235723</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="C9">
+        <v>0.33366602070370999</v>
+      </c>
+      <c r="D9">
+        <v>0.35583697664777802</v>
+      </c>
+      <c r="E9">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F9">
+        <v>0.93769350180261202</v>
+      </c>
+      <c r="G9">
+        <v>0.83052242823572298</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>80</v>
       </c>
       <c r="B10" t="s">
         <v>30</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.423448090808604</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.355836976647778</v>
-      </c>
-      <c r="E10" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1.19000586953545</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0.830522428235723</v>
-      </c>
-    </row>
-    <row r="11">
+      <c r="C10">
+        <v>0.42344809080860402</v>
+      </c>
+      <c r="D10">
+        <v>0.35583697664777802</v>
+      </c>
+      <c r="E10">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F10">
+        <v>1.1900058695354501</v>
+      </c>
+      <c r="G10">
+        <v>0.83052242823572298</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>81</v>
       </c>
       <c r="B11" t="s">
         <v>30</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.0765519091913996</v>
-      </c>
-      <c r="D11" t="n">
-        <v>0.355836976647779</v>
-      </c>
-      <c r="E11" t="n">
+      <c r="C11">
+        <v>7.6551909191399606E-2</v>
+      </c>
+      <c r="D11">
+        <v>0.35583697664777902</v>
+      </c>
+      <c r="E11">
         <v>51</v>
       </c>
-      <c r="F11" t="n">
-        <v>0.215131968331593</v>
-      </c>
-      <c r="G11" t="n">
-        <v>0.830522428235723</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="F11">
+        <v>0.21513196833159301</v>
+      </c>
+      <c r="G11">
+        <v>0.83052242823572298</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>82</v>
       </c>
       <c r="B12" t="s">
         <v>30</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.166333979296294</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.355836976647778</v>
-      </c>
-      <c r="E12" t="n">
+      <c r="C12">
+        <v>0.16633397929629401</v>
+      </c>
+      <c r="D12">
+        <v>0.35583697664777802</v>
+      </c>
+      <c r="E12">
         <v>51</v>
       </c>
-      <c r="F12" t="n">
-        <v>0.467444336064427</v>
-      </c>
-      <c r="G12" t="n">
-        <v>0.830522428235723</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="F12">
+        <v>0.46744433606442698</v>
+      </c>
+      <c r="G12">
+        <v>0.83052242823572298</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>83</v>
       </c>
       <c r="B13" t="s">
         <v>30</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.0897820701048941</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.355836976647778</v>
-      </c>
-      <c r="E13" t="n">
+      <c r="C13">
+        <v>8.9782070104894099E-2</v>
+      </c>
+      <c r="D13">
+        <v>0.35583697664777802</v>
+      </c>
+      <c r="E13">
         <v>51</v>
       </c>
-      <c r="F13" t="n">
+      <c r="F13">
         <v>0.252312367732834</v>
       </c>
-      <c r="G13" t="n">
-        <v>0.830522428235723</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="G13">
+        <v>0.83052242823572298</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>78</v>
       </c>
       <c r="B14" t="s">
         <v>35</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.570436980025377</v>
-      </c>
-      <c r="D14" t="n">
+      <c r="C14">
+        <v>0.57043698002537702</v>
+      </c>
+      <c r="D14">
         <v>0.268987470711749</v>
       </c>
-      <c r="E14" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F14" t="n">
-        <v>2.12068234448238</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.116492770998788</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="E14">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F14">
+        <v>2.1206823444823799</v>
+      </c>
+      <c r="G14">
+        <v>0.11649277099878801</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>79</v>
       </c>
       <c r="B15" t="s">
         <v>35</v>
       </c>
-      <c r="C15" t="n">
-        <v>-0.0482744571466142</v>
-      </c>
-      <c r="D15" t="n">
+      <c r="C15">
+        <v>-4.82744571466142E-2</v>
+      </c>
+      <c r="D15">
         <v>0.268987470711749</v>
       </c>
-      <c r="E15" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.179467307599416</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.858281921729342</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="E15">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F15">
+        <v>-0.17946730759941601</v>
+      </c>
+      <c r="G15">
+        <v>0.85828192172934203</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>80</v>
       </c>
       <c r="B16" t="s">
         <v>35</v>
       </c>
-      <c r="C16" t="n">
+      <c r="C16">
         <v>0.472856758837292</v>
       </c>
-      <c r="D16" t="n">
+      <c r="D16">
         <v>0.268987470711749</v>
       </c>
-      <c r="E16" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1.75791369607699</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.12714397920857</v>
-      </c>
-    </row>
-    <row r="17">
+      <c r="E16">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F16">
+        <v>1.7579136960769901</v>
+      </c>
+      <c r="G16">
+        <v>0.12714397920857001</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>81</v>
       </c>
       <c r="B17" t="s">
         <v>35</v>
       </c>
-      <c r="C17" t="n">
-        <v>-0.618711437171992</v>
-      </c>
-      <c r="D17" t="n">
+      <c r="C17">
+        <v>-0.61871143717199195</v>
+      </c>
+      <c r="D17">
         <v>0.268987470711749</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E17">
         <v>51</v>
       </c>
-      <c r="F17" t="n">
-        <v>-2.3001496520818</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.116492770998788</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="F17">
+        <v>-2.3001496520817999</v>
+      </c>
+      <c r="G17">
+        <v>0.11649277099878801</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>82</v>
       </c>
       <c r="B18" t="s">
         <v>35</v>
       </c>
-      <c r="C18" t="n">
-        <v>-0.0975802211880858</v>
-      </c>
-      <c r="D18" t="n">
+      <c r="C18">
+        <v>-9.7580221188085806E-2</v>
+      </c>
+      <c r="D18">
         <v>0.268987470711749</v>
       </c>
-      <c r="E18" t="n">
+      <c r="E18">
         <v>51</v>
       </c>
-      <c r="F18" t="n">
-        <v>-0.362768648405391</v>
-      </c>
-      <c r="G18" t="n">
-        <v>0.858281921729342</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="F18">
+        <v>-0.36276864840539103</v>
+      </c>
+      <c r="G18">
+        <v>0.85828192172934203</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>83</v>
       </c>
       <c r="B19" t="s">
         <v>35</v>
       </c>
-      <c r="C19" t="n">
-        <v>0.521131215983906</v>
-      </c>
-      <c r="D19" t="n">
+      <c r="C19">
+        <v>0.52113121598390599</v>
+      </c>
+      <c r="D19">
         <v>0.268987470711749</v>
       </c>
-      <c r="E19" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F19" t="n">
-        <v>1.93738100367641</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0.116492770998788</v>
-      </c>
-    </row>
-    <row r="20">
+      <c r="E19">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F19">
+        <v>1.9373810036764101</v>
+      </c>
+      <c r="G19">
+        <v>0.11649277099878801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>78</v>
       </c>
       <c r="B20" t="s">
         <v>43</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20">
         <v>0.271009863934635</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.410885148510435</v>
-      </c>
-      <c r="E20" t="n">
+      <c r="D20">
+        <v>0.41088514851043501</v>
+      </c>
+      <c r="E20">
         <v>51</v>
       </c>
-      <c r="F20" t="n">
-        <v>0.659575710918529</v>
-      </c>
-      <c r="G20" t="n">
-        <v>0.512493740416351</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="F20">
+        <v>0.65957571091852896</v>
+      </c>
+      <c r="G20">
+        <v>0.51249374041635098</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>79</v>
       </c>
       <c r="B21" t="s">
         <v>43</v>
       </c>
-      <c r="C21" t="n">
-        <v>-1.8857446059221</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.410885148510435</v>
-      </c>
-      <c r="E21" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F21" t="n">
-        <v>-4.58946888871114</v>
-      </c>
-      <c r="G21" t="n">
-        <v>0.0000878123731676433</v>
-      </c>
-    </row>
-    <row r="22">
+      <c r="C21">
+        <v>-1.8857446059220999</v>
+      </c>
+      <c r="D21">
+        <v>0.41088514851043501</v>
+      </c>
+      <c r="E21">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F21">
+        <v>-4.5894688887111403</v>
+      </c>
+      <c r="G21">
+        <v>8.7812373167643303E-5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>80</v>
       </c>
       <c r="B22" t="s">
         <v>43</v>
       </c>
-      <c r="C22" t="n">
-        <v>-1.55033518679534</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.410885148510435</v>
-      </c>
-      <c r="E22" t="n">
-        <v>50.9999999999999</v>
-      </c>
-      <c r="F22" t="n">
-        <v>-3.77315946418531</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.000631676820686117</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22">
+        <v>-1.5503351867953401</v>
+      </c>
+      <c r="D22">
+        <v>0.41088514851043501</v>
+      </c>
+      <c r="E22">
+        <v>50.999999999999901</v>
+      </c>
+      <c r="F22">
+        <v>-3.7731594641853099</v>
+      </c>
+      <c r="G22">
+        <v>6.3167682068611701E-4</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>81</v>
       </c>
       <c r="B23" t="s">
         <v>43</v>
       </c>
-      <c r="C23" t="n">
-        <v>-2.15675446985673</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.410885148510435</v>
-      </c>
-      <c r="E23" t="n">
+      <c r="C23">
+        <v>-2.1567544698567298</v>
+      </c>
+      <c r="D23">
+        <v>0.41088514851043501</v>
+      </c>
+      <c r="E23">
         <v>51</v>
       </c>
-      <c r="F23" t="n">
-        <v>-5.24904459962966</v>
-      </c>
-      <c r="G23" t="n">
-        <v>0.0000179503790377461</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="F23">
+        <v>-5.2490445996296602</v>
+      </c>
+      <c r="G23">
+        <v>1.7950379037746102E-5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>82</v>
       </c>
       <c r="B24" t="s">
         <v>43</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C24">
         <v>-1.82134505072997</v>
       </c>
-      <c r="D24" t="n">
-        <v>0.410885148510435</v>
-      </c>
-      <c r="E24" t="n">
+      <c r="D24">
+        <v>0.41088514851043501</v>
+      </c>
+      <c r="E24">
         <v>51</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F24">
         <v>-4.43273517510384</v>
       </c>
-      <c r="G24" t="n">
-        <v>0.0000992076242953488</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="G24">
+        <v>9.9207624295348802E-5</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>83</v>
       </c>
       <c r="B25" t="s">
         <v>43</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.335409419126761</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.410885148510435</v>
-      </c>
-      <c r="E25" t="n">
+      <c r="C25">
+        <v>0.33540941912676098</v>
+      </c>
+      <c r="D25">
+        <v>0.41088514851043501</v>
+      </c>
+      <c r="E25">
         <v>51</v>
       </c>
-      <c r="F25" t="n">
+      <c r="F25">
         <v>0.816309424525825</v>
       </c>
-      <c r="G25" t="n">
-        <v>0.501743773031014</v>
+      <c r="G25">
+        <v>0.50174377303101403</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
 </file>